--- a/data/nzd0329/nzd0329.xlsx
+++ b/data/nzd0329/nzd0329.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O511"/>
+  <dimension ref="A1:O513"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26337,13 +26337,13 @@
         <v>298.07</v>
       </c>
       <c r="E511" t="n">
-        <v>307.56</v>
+        <v>311.92</v>
       </c>
       <c r="F511" t="n">
-        <v>297.88</v>
+        <v>303.94</v>
       </c>
       <c r="G511" t="n">
-        <v>387.78</v>
+        <v>383.91</v>
       </c>
       <c r="H511" t="n">
         <v>372.24</v>
@@ -26369,6 +26369,108 @@
       <c r="O511" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:19:36+00:00</t>
+        </is>
+      </c>
+      <c r="B512" t="n">
+        <v>370.61</v>
+      </c>
+      <c r="C512" t="n">
+        <v>377.49</v>
+      </c>
+      <c r="D512" t="n">
+        <v>320.6</v>
+      </c>
+      <c r="E512" t="n">
+        <v>340.48</v>
+      </c>
+      <c r="F512" t="n">
+        <v>311.03</v>
+      </c>
+      <c r="G512" t="n">
+        <v>381.4</v>
+      </c>
+      <c r="H512" t="n">
+        <v>373.49</v>
+      </c>
+      <c r="I512" t="n">
+        <v>375.13</v>
+      </c>
+      <c r="J512" t="n">
+        <v>371.22</v>
+      </c>
+      <c r="K512" t="n">
+        <v>373.41</v>
+      </c>
+      <c r="L512" t="n">
+        <v>370.49</v>
+      </c>
+      <c r="M512" t="n">
+        <v>364.53</v>
+      </c>
+      <c r="N512" t="n">
+        <v>371.32</v>
+      </c>
+      <c r="O512" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-16 22:13:32+00:00</t>
+        </is>
+      </c>
+      <c r="B513" t="n">
+        <v>383.51</v>
+      </c>
+      <c r="C513" t="n">
+        <v>385.91</v>
+      </c>
+      <c r="D513" t="n">
+        <v>332.39</v>
+      </c>
+      <c r="E513" t="n">
+        <v>354.34</v>
+      </c>
+      <c r="F513" t="n">
+        <v>318.34</v>
+      </c>
+      <c r="G513" t="n">
+        <v>382.35</v>
+      </c>
+      <c r="H513" t="n">
+        <v>376.38</v>
+      </c>
+      <c r="I513" t="n">
+        <v>377.32</v>
+      </c>
+      <c r="J513" t="n">
+        <v>374.2</v>
+      </c>
+      <c r="K513" t="n">
+        <v>376.83</v>
+      </c>
+      <c r="L513" t="n">
+        <v>374.65</v>
+      </c>
+      <c r="M513" t="n">
+        <v>367.84</v>
+      </c>
+      <c r="N513" t="n">
+        <v>372.87</v>
+      </c>
+      <c r="O513" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -26383,7 +26485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B535"/>
+  <dimension ref="A1:B537"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31736,6 +31838,26 @@
       </c>
       <c r="B535" t="n">
         <v>-0.99</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B536" t="n">
+        <v>-0.12</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>2026-01-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B537" t="n">
+        <v>0.9399999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -31904,28 +32026,28 @@
         <v>0.06519999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.398774253490514</v>
+        <v>-1.415237775240129</v>
       </c>
       <c r="J2" t="n">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="K2" t="n">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5261675405051356</v>
+        <v>0.5285694002613939</v>
       </c>
       <c r="M2" t="n">
-        <v>7.916802281341769</v>
+        <v>8.012171783575219</v>
       </c>
       <c r="N2" t="n">
-        <v>105.7594880877099</v>
+        <v>107.6296735210996</v>
       </c>
       <c r="O2" t="n">
-        <v>10.2839432168653</v>
+        <v>10.37447220445935</v>
       </c>
       <c r="P2" t="n">
-        <v>437.3835662884446</v>
+        <v>437.548131218601</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -31982,28 +32104,28 @@
         <v>0.0912</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.441683439647493</v>
+        <v>-1.44233267356092</v>
       </c>
       <c r="J3" t="n">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="K3" t="n">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4033255522171892</v>
+        <v>0.4052929474784319</v>
       </c>
       <c r="M3" t="n">
-        <v>10.4615832186432</v>
+        <v>10.43769152219574</v>
       </c>
       <c r="N3" t="n">
-        <v>185.6501435172332</v>
+        <v>184.998713490122</v>
       </c>
       <c r="O3" t="n">
-        <v>13.62534929890728</v>
+        <v>13.60142321560953</v>
       </c>
       <c r="P3" t="n">
-        <v>420.6895262860011</v>
+        <v>420.6959516833643</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32060,28 +32182,28 @@
         <v>0.081</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.678050801324259</v>
+        <v>-1.701109815328604</v>
       </c>
       <c r="J4" t="n">
+        <v>512</v>
+      </c>
+      <c r="K4" t="n">
         <v>510</v>
       </c>
-      <c r="K4" t="n">
-        <v>508</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.1071383420731875</v>
+        <v>0.1102267505233134</v>
       </c>
       <c r="M4" t="n">
-        <v>29.92723572863689</v>
+        <v>29.95800857530368</v>
       </c>
       <c r="N4" t="n">
-        <v>1421.253817248543</v>
+        <v>1420.028391911993</v>
       </c>
       <c r="O4" t="n">
-        <v>37.69952011960554</v>
+        <v>37.68326408250741</v>
       </c>
       <c r="P4" t="n">
-        <v>403.7403627340863</v>
+        <v>403.9695426004321</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32138,28 +32260,28 @@
         <v>0.06569999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.436238811099318</v>
+        <v>-2.433928636867857</v>
       </c>
       <c r="J5" t="n">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="K5" t="n">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2110380578215773</v>
+        <v>0.2120669822963377</v>
       </c>
       <c r="M5" t="n">
-        <v>29.04618410644023</v>
+        <v>28.94757327579138</v>
       </c>
       <c r="N5" t="n">
-        <v>1309.097345986991</v>
+        <v>1303.450723066709</v>
       </c>
       <c r="O5" t="n">
-        <v>36.18145030242695</v>
+        <v>36.10333396054593</v>
       </c>
       <c r="P5" t="n">
-        <v>410.6650995874919</v>
+        <v>410.6416426252912</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32216,28 +32338,28 @@
         <v>0.0479</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8247488519393683</v>
+        <v>-0.8689205189078396</v>
       </c>
       <c r="J6" t="n">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="K6" t="n">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="L6" t="n">
-        <v>0.05896395359928364</v>
+        <v>0.06412360992614363</v>
       </c>
       <c r="M6" t="n">
-        <v>15.5122223510583</v>
+        <v>15.83778335012471</v>
       </c>
       <c r="N6" t="n">
-        <v>640.9520508698366</v>
+        <v>652.9972667245397</v>
       </c>
       <c r="O6" t="n">
-        <v>25.31703084624729</v>
+        <v>25.5538111976382</v>
       </c>
       <c r="P6" t="n">
-        <v>400.7364513533737</v>
+        <v>401.1873893795299</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32294,28 +32416,28 @@
         <v>0.0721</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.7387500649238097</v>
+        <v>-0.7398830378828771</v>
       </c>
       <c r="J7" t="n">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="K7" t="n">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1360632836595981</v>
+        <v>0.1373660936562519</v>
       </c>
       <c r="M7" t="n">
-        <v>8.501308028373575</v>
+        <v>8.461770301897833</v>
       </c>
       <c r="N7" t="n">
-        <v>208.4338590133866</v>
+        <v>207.5452982315338</v>
       </c>
       <c r="O7" t="n">
-        <v>14.43723862147421</v>
+        <v>14.40643252965611</v>
       </c>
       <c r="P7" t="n">
-        <v>401.0648895313425</v>
+        <v>401.0761568041978</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -32372,28 +32494,28 @@
         <v>0.0625</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.8838323707223547</v>
+        <v>-0.8845689216136676</v>
       </c>
       <c r="J8" t="n">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="K8" t="n">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3360024109242296</v>
+        <v>0.3380642742421278</v>
       </c>
       <c r="M8" t="n">
-        <v>6.981731244364381</v>
+        <v>6.960331510182761</v>
       </c>
       <c r="N8" t="n">
-        <v>92.01215692529225</v>
+        <v>91.6611734569161</v>
       </c>
       <c r="O8" t="n">
-        <v>9.592296749230199</v>
+        <v>9.573984199742346</v>
       </c>
       <c r="P8" t="n">
-        <v>399.3058076041613</v>
+        <v>399.3132172325828</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -32450,28 +32572,28 @@
         <v>0.1418</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.9697451403608567</v>
+        <v>-0.9642831023975964</v>
       </c>
       <c r="J9" t="n">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="K9" t="n">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4310924526662189</v>
+        <v>0.4294247340067771</v>
       </c>
       <c r="M9" t="n">
-        <v>6.112211413451527</v>
+        <v>6.11747521709285</v>
       </c>
       <c r="N9" t="n">
-        <v>74.31187602778442</v>
+        <v>74.25634533424822</v>
       </c>
       <c r="O9" t="n">
-        <v>8.620433633395969</v>
+        <v>8.617212155578406</v>
       </c>
       <c r="P9" t="n">
-        <v>394.0982759618854</v>
+        <v>394.0434695068572</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -32528,28 +32650,28 @@
         <v>0.1123</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.8832145477351175</v>
+        <v>-0.8805003308556585</v>
       </c>
       <c r="J10" t="n">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="K10" t="n">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4116600367346058</v>
+        <v>0.4117905835643004</v>
       </c>
       <c r="M10" t="n">
-        <v>6.106606302983073</v>
+        <v>6.096905034457613</v>
       </c>
       <c r="N10" t="n">
-        <v>66.7565361535879</v>
+        <v>66.55997958662877</v>
       </c>
       <c r="O10" t="n">
-        <v>8.170467315495969</v>
+        <v>8.158429970688525</v>
       </c>
       <c r="P10" t="n">
-        <v>392.186635263111</v>
+        <v>392.1593925044307</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -32606,28 +32728,28 @@
         <v>0.0985</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.9096051157102979</v>
+        <v>-0.9124300259884162</v>
       </c>
       <c r="J11" t="n">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="K11" t="n">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="L11" t="n">
-        <v>0.301407871374781</v>
+        <v>0.3042041356262358</v>
       </c>
       <c r="M11" t="n">
-        <v>8.29463499581442</v>
+        <v>8.279453467550383</v>
       </c>
       <c r="N11" t="n">
-        <v>114.8276857712968</v>
+        <v>114.4496418246731</v>
       </c>
       <c r="O11" t="n">
-        <v>10.71576809058953</v>
+        <v>10.69811393773094</v>
       </c>
       <c r="P11" t="n">
-        <v>403.1253880305642</v>
+        <v>403.1537137699507</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -32684,28 +32806,28 @@
         <v>0.1001</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.9995297763772679</v>
+        <v>-1.006579623714276</v>
       </c>
       <c r="J12" t="n">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="K12" t="n">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2904697000514832</v>
+        <v>0.2944071780144027</v>
       </c>
       <c r="M12" t="n">
-        <v>9.577066942144757</v>
+        <v>9.582554236622267</v>
       </c>
       <c r="N12" t="n">
-        <v>145.544281742775</v>
+        <v>145.3700379375396</v>
       </c>
       <c r="O12" t="n">
-        <v>12.06417347947115</v>
+        <v>12.05694977751586</v>
       </c>
       <c r="P12" t="n">
-        <v>408.8630024554323</v>
+        <v>408.9339073631265</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -32762,28 +32884,28 @@
         <v>0.137</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.7541264023979574</v>
+        <v>-0.7616727512347121</v>
       </c>
       <c r="J13" t="n">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="K13" t="n">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2072829890879619</v>
+        <v>0.2112722218841655</v>
       </c>
       <c r="M13" t="n">
-        <v>8.743245367710344</v>
+        <v>8.757452733458411</v>
       </c>
       <c r="N13" t="n">
-        <v>129.465350760313</v>
+        <v>129.404628192121</v>
       </c>
       <c r="O13" t="n">
-        <v>11.37828417470372</v>
+        <v>11.37561550827563</v>
       </c>
       <c r="P13" t="n">
-        <v>396.7056033552765</v>
+        <v>396.7817727341779</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -32840,28 +32962,28 @@
         <v>0.1005</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.9082962336834441</v>
+        <v>-0.9104129411652003</v>
       </c>
       <c r="J14" t="n">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="K14" t="n">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="L14" t="n">
-        <v>0.3107187174316683</v>
+        <v>0.3132934686265222</v>
       </c>
       <c r="M14" t="n">
-        <v>8.152693343504959</v>
+        <v>8.133953827619308</v>
       </c>
       <c r="N14" t="n">
-        <v>109.6109786686173</v>
+        <v>109.2143660906688</v>
       </c>
       <c r="O14" t="n">
-        <v>10.46952619121884</v>
+        <v>10.45056774011196</v>
       </c>
       <c r="P14" t="n">
-        <v>399.0565002056522</v>
+        <v>399.0777639825352</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -32899,7 +33021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O511"/>
+  <dimension ref="A1:O513"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71903,17 +72025,17 @@
       </c>
       <c r="E511" t="inlineStr">
         <is>
-          <t>-40.95534039973704,172.10093458655416</t>
+          <t>-40.9553484606368,172.10088388598018</t>
         </is>
       </c>
       <c r="F511" t="inlineStr">
         <is>
-          <t>-40.95465952135832,172.10085654196976</t>
+          <t>-40.9546707252618,172.10078607354436</t>
         </is>
       </c>
       <c r="G511" t="inlineStr">
         <is>
-          <t>-40.95416273730314,172.0996205427502</t>
+          <t>-40.954155582768244,172.09966554463114</t>
         </is>
       </c>
       <c r="H511" t="inlineStr">
@@ -71954,6 +72076,160 @@
       <c r="O511" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:19:36+00:00</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>-40.9574458737652,172.10077320653102</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>-40.95679563085822,172.1005025992485</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>-40.956027483645656,172.10097355648097</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>-40.955401262673,172.10055177366792</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>-40.95468383340408,172.100703627783</t>
+        </is>
+      </c>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>-40.95415094247905,172.09969473189255</t>
+        </is>
+      </c>
+      <c r="H512" t="inlineStr">
+        <is>
+          <t>-40.95347332322748,172.09959611189592</t>
+        </is>
+      </c>
+      <c r="I512" t="inlineStr">
+        <is>
+          <t>-40.9528083466991,172.09938529087907</t>
+        </is>
+      </c>
+      <c r="J512" t="inlineStr">
+        <is>
+          <t>-40.95212413739271,172.0992803231358</t>
+        </is>
+      </c>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>-40.951445907605205,172.09915892546096</t>
+        </is>
+      </c>
+      <c r="L512" t="inlineStr">
+        <is>
+          <t>-40.95076863472077,172.0990986058541</t>
+        </is>
+      </c>
+      <c r="M512" t="inlineStr">
+        <is>
+          <t>-40.95008865360536,172.09907422636988</t>
+        </is>
+      </c>
+      <c r="N512" t="inlineStr">
+        <is>
+          <t>-40.94941999527316,172.0988991083188</t>
+        </is>
+      </c>
+      <c r="O512" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-16 22:13:32+00:00</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>-40.95746972310217,172.10062319301628</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>-40.956811197490275,172.10040468438103</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>-40.95604928125854,172.10083645415543</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>-40.955426886843604,172.10039060133155</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>-40.954697348224904,172.10061862372797</t>
+        </is>
+      </c>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>-40.95415269876469,172.09968368492156</t>
+        </is>
+      </c>
+      <c r="H513" t="inlineStr">
+        <is>
+          <t>-40.953478666023145,172.09956250618774</t>
+        </is>
+      </c>
+      <c r="I513" t="inlineStr">
+        <is>
+          <t>-40.95281194167905,172.09935970702918</t>
+        </is>
+      </c>
+      <c r="J513" t="inlineStr">
+        <is>
+          <t>-40.95212759788134,172.09924521332698</t>
+        </is>
+      </c>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>-40.9514489466317,172.09911849120348</t>
+        </is>
+      </c>
+      <c r="L513" t="inlineStr">
+        <is>
+          <t>-40.95077233130497,172.09904942316533</t>
+        </is>
+      </c>
+      <c r="M513" t="inlineStr">
+        <is>
+          <t>-40.95009159488582,172.09903509343144</t>
+        </is>
+      </c>
+      <c r="N513" t="inlineStr">
+        <is>
+          <t>-40.949421372590464,172.0988807834098</t>
+        </is>
+      </c>
+      <c r="O513" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>

--- a/data/nzd0329/nzd0329.xlsx
+++ b/data/nzd0329/nzd0329.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O513"/>
+  <dimension ref="A1:O515"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26474,6 +26474,108 @@
         </is>
       </c>
     </row>
+    <row r="514">
+      <c r="A514" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-31 22:19:26+00:00</t>
+        </is>
+      </c>
+      <c r="B514" t="n">
+        <v>394.09</v>
+      </c>
+      <c r="C514" t="n">
+        <v>394.86</v>
+      </c>
+      <c r="D514" t="n">
+        <v>376.24</v>
+      </c>
+      <c r="E514" t="n">
+        <v>375.92</v>
+      </c>
+      <c r="F514" t="n">
+        <v>345.31</v>
+      </c>
+      <c r="G514" t="n">
+        <v>383.7</v>
+      </c>
+      <c r="H514" t="n">
+        <v>379.15</v>
+      </c>
+      <c r="I514" t="n">
+        <v>378.43</v>
+      </c>
+      <c r="J514" t="n">
+        <v>376.13</v>
+      </c>
+      <c r="K514" t="n">
+        <v>379.49</v>
+      </c>
+      <c r="L514" t="n">
+        <v>377.12</v>
+      </c>
+      <c r="M514" t="n">
+        <v>369.61</v>
+      </c>
+      <c r="N514" t="n">
+        <v>372.84</v>
+      </c>
+      <c r="O514" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-08 22:19:13+00:00</t>
+        </is>
+      </c>
+      <c r="B515" t="n">
+        <v>408.21</v>
+      </c>
+      <c r="C515" t="n">
+        <v>403.74</v>
+      </c>
+      <c r="D515" t="n">
+        <v>401.2</v>
+      </c>
+      <c r="E515" t="n">
+        <v>398.15</v>
+      </c>
+      <c r="F515" t="n">
+        <v>373.27</v>
+      </c>
+      <c r="G515" t="n">
+        <v>381.83</v>
+      </c>
+      <c r="H515" t="n">
+        <v>376.43</v>
+      </c>
+      <c r="I515" t="n">
+        <v>377.16</v>
+      </c>
+      <c r="J515" t="n">
+        <v>377.13</v>
+      </c>
+      <c r="K515" t="n">
+        <v>381.6</v>
+      </c>
+      <c r="L515" t="n">
+        <v>378.99</v>
+      </c>
+      <c r="M515" t="n">
+        <v>372.11</v>
+      </c>
+      <c r="N515" t="n">
+        <v>375.09</v>
+      </c>
+      <c r="O515" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -26485,7 +26587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B537"/>
+  <dimension ref="A1:B539"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31858,6 +31960,26 @@
       </c>
       <c r="B537" t="n">
         <v>0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>2026-01-31 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B538" t="n">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>2026-02-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B539" t="n">
+        <v>-0.72</v>
       </c>
     </row>
   </sheetData>
@@ -32026,28 +32148,28 @@
         <v>0.06519999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.415237775240129</v>
+        <v>-1.414491776411109</v>
       </c>
       <c r="J2" t="n">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="K2" t="n">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5285694002613939</v>
+        <v>0.5297548929566195</v>
       </c>
       <c r="M2" t="n">
-        <v>8.012171783575219</v>
+        <v>8.006950597554813</v>
       </c>
       <c r="N2" t="n">
-        <v>107.6296735210996</v>
+        <v>107.4095398788242</v>
       </c>
       <c r="O2" t="n">
-        <v>10.37447220445935</v>
+        <v>10.36385738414149</v>
       </c>
       <c r="P2" t="n">
-        <v>437.548131218601</v>
+        <v>437.5406155146625</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -32104,28 +32226,28 @@
         <v>0.0912</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.44233267356092</v>
+        <v>-1.430632528892325</v>
       </c>
       <c r="J3" t="n">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="K3" t="n">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4052929474784319</v>
+        <v>0.4017035214776845</v>
       </c>
       <c r="M3" t="n">
-        <v>10.43769152219574</v>
+        <v>10.45490331844135</v>
       </c>
       <c r="N3" t="n">
-        <v>184.998713490122</v>
+        <v>185.4393454753076</v>
       </c>
       <c r="O3" t="n">
-        <v>13.60142321560953</v>
+        <v>13.61761159217385</v>
       </c>
       <c r="P3" t="n">
-        <v>420.6959516833643</v>
+        <v>420.5790499549053</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32182,28 +32304,28 @@
         <v>0.081</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.701109815328604</v>
+        <v>-1.680352237643689</v>
       </c>
       <c r="J4" t="n">
+        <v>514</v>
+      </c>
+      <c r="K4" t="n">
         <v>512</v>
       </c>
-      <c r="K4" t="n">
-        <v>510</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.1102267505233134</v>
+        <v>0.1083034791317263</v>
       </c>
       <c r="M4" t="n">
-        <v>29.95800857530368</v>
+        <v>29.93934708981162</v>
       </c>
       <c r="N4" t="n">
-        <v>1420.028391911993</v>
+        <v>1418.516067876993</v>
       </c>
       <c r="O4" t="n">
-        <v>37.68326408250741</v>
+        <v>37.66319248121424</v>
       </c>
       <c r="P4" t="n">
-        <v>403.9695426004321</v>
+        <v>403.7623409208229</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32260,28 +32382,28 @@
         <v>0.06569999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.433928636867857</v>
+        <v>-2.404767662020911</v>
       </c>
       <c r="J5" t="n">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="K5" t="n">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2120669822963377</v>
+        <v>0.2084504355969674</v>
       </c>
       <c r="M5" t="n">
-        <v>28.94757327579138</v>
+        <v>28.96509489161581</v>
       </c>
       <c r="N5" t="n">
-        <v>1303.450723066709</v>
+        <v>1305.303097812725</v>
       </c>
       <c r="O5" t="n">
-        <v>36.10333396054593</v>
+        <v>36.12897864336502</v>
       </c>
       <c r="P5" t="n">
-        <v>410.6416426252912</v>
+        <v>410.344001785999</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32338,28 +32460,28 @@
         <v>0.0479</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8689205189078396</v>
+        <v>-0.8824715120398344</v>
       </c>
       <c r="J6" t="n">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="K6" t="n">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="L6" t="n">
-        <v>0.06412360992614363</v>
+        <v>0.066271949909952</v>
       </c>
       <c r="M6" t="n">
-        <v>15.83778335012471</v>
+        <v>15.8937205494129</v>
       </c>
       <c r="N6" t="n">
-        <v>652.9972667245397</v>
+        <v>652.5785522484844</v>
       </c>
       <c r="O6" t="n">
-        <v>25.5538111976382</v>
+        <v>25.54561708490293</v>
       </c>
       <c r="P6" t="n">
-        <v>401.1873893795299</v>
+        <v>401.3261759644096</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32416,28 +32538,28 @@
         <v>0.0721</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.7398830378828771</v>
+        <v>-0.7389891040225955</v>
       </c>
       <c r="J7" t="n">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="K7" t="n">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1373660936562519</v>
+        <v>0.1379825255388661</v>
       </c>
       <c r="M7" t="n">
-        <v>8.461770301897833</v>
+        <v>8.433464613591648</v>
       </c>
       <c r="N7" t="n">
-        <v>207.5452982315338</v>
+        <v>206.7362769566301</v>
       </c>
       <c r="O7" t="n">
-        <v>14.40643252965611</v>
+        <v>14.37832663965561</v>
       </c>
       <c r="P7" t="n">
-        <v>401.0761568041978</v>
+        <v>401.0671700799081</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -32494,28 +32616,28 @@
         <v>0.0625</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.8845689216136676</v>
+        <v>-0.8832355365598811</v>
       </c>
       <c r="J8" t="n">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="K8" t="n">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3380642742421278</v>
+        <v>0.3390586134043804</v>
       </c>
       <c r="M8" t="n">
-        <v>6.960331510182761</v>
+        <v>6.939542764779969</v>
       </c>
       <c r="N8" t="n">
-        <v>91.6611734569161</v>
+        <v>91.32133368392169</v>
       </c>
       <c r="O8" t="n">
-        <v>9.573984199742346</v>
+        <v>9.556219633512077</v>
       </c>
       <c r="P8" t="n">
-        <v>399.3132172325828</v>
+        <v>399.2997346590754</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -32572,28 +32694,28 @@
         <v>0.1418</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.9642831023975964</v>
+        <v>-0.9577580758980658</v>
       </c>
       <c r="J9" t="n">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="K9" t="n">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4294247340067771</v>
+        <v>0.4268739963281787</v>
       </c>
       <c r="M9" t="n">
-        <v>6.11747521709285</v>
+        <v>6.128732887835938</v>
       </c>
       <c r="N9" t="n">
-        <v>74.25634533424822</v>
+        <v>74.29997564751309</v>
       </c>
       <c r="O9" t="n">
-        <v>8.617212155578406</v>
+        <v>8.619743363204794</v>
       </c>
       <c r="P9" t="n">
-        <v>394.0434695068572</v>
+        <v>393.9777590695945</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -32650,28 +32772,28 @@
         <v>0.1123</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.8805003308556585</v>
+        <v>-0.8750277927882016</v>
       </c>
       <c r="J10" t="n">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="K10" t="n">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4117905835643004</v>
+        <v>0.4097730481325257</v>
       </c>
       <c r="M10" t="n">
-        <v>6.096905034457613</v>
+        <v>6.101617802579074</v>
       </c>
       <c r="N10" t="n">
-        <v>66.55997958662877</v>
+        <v>66.53435543487245</v>
       </c>
       <c r="O10" t="n">
-        <v>8.158429970688525</v>
+        <v>8.156859410022491</v>
       </c>
       <c r="P10" t="n">
-        <v>392.1593925044307</v>
+        <v>392.1042770857853</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -32728,28 +32850,28 @@
         <v>0.0985</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.9124300259884162</v>
+        <v>-0.9113455485687177</v>
       </c>
       <c r="J11" t="n">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="K11" t="n">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3042041356262358</v>
+        <v>0.3053016301149624</v>
       </c>
       <c r="M11" t="n">
-        <v>8.279453467550383</v>
+        <v>8.252297022212604</v>
       </c>
       <c r="N11" t="n">
-        <v>114.4496418246731</v>
+        <v>114.0144567515605</v>
       </c>
       <c r="O11" t="n">
-        <v>10.69811393773094</v>
+        <v>10.67775522998914</v>
       </c>
       <c r="P11" t="n">
-        <v>403.1537137699507</v>
+        <v>403.1427878787277</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -32806,28 +32928,28 @@
         <v>0.1001</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.006579623714276</v>
+        <v>-1.009582936911454</v>
       </c>
       <c r="J12" t="n">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="K12" t="n">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2944071780144027</v>
+        <v>0.2971509980079566</v>
       </c>
       <c r="M12" t="n">
-        <v>9.582554236622267</v>
+        <v>9.563246681902427</v>
       </c>
       <c r="N12" t="n">
-        <v>145.3700379375396</v>
+        <v>144.8711953936578</v>
       </c>
       <c r="O12" t="n">
-        <v>12.05694977751586</v>
+        <v>12.03624507035553</v>
       </c>
       <c r="P12" t="n">
-        <v>408.9339073631265</v>
+        <v>408.9642331645847</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -32884,28 +33006,28 @@
         <v>0.137</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.7616727512347121</v>
+        <v>-0.7657516345549075</v>
       </c>
       <c r="J13" t="n">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="K13" t="n">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2112722218841655</v>
+        <v>0.2141710183429203</v>
       </c>
       <c r="M13" t="n">
-        <v>8.757452733458411</v>
+        <v>8.74924731258862</v>
       </c>
       <c r="N13" t="n">
-        <v>129.404628192121</v>
+        <v>129.0298843961183</v>
       </c>
       <c r="O13" t="n">
-        <v>11.37561550827563</v>
+        <v>11.35913220259885</v>
       </c>
       <c r="P13" t="n">
-        <v>396.7817727341779</v>
+        <v>396.8231040614628</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -32962,28 +33084,28 @@
         <v>0.1005</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.9104129411652003</v>
+        <v>-0.9111261466392545</v>
       </c>
       <c r="J14" t="n">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="K14" t="n">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="L14" t="n">
-        <v>0.3132934686265222</v>
+        <v>0.3152659201614775</v>
       </c>
       <c r="M14" t="n">
-        <v>8.133953827619308</v>
+        <v>8.106921717804227</v>
       </c>
       <c r="N14" t="n">
-        <v>109.2143660906688</v>
+        <v>108.7926264590571</v>
       </c>
       <c r="O14" t="n">
-        <v>10.45056774011196</v>
+        <v>10.43037038935134</v>
       </c>
       <c r="P14" t="n">
-        <v>399.0777639825352</v>
+        <v>399.0849540812324</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -33021,7 +33143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O513"/>
+  <dimension ref="A1:O515"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72233,6 +72355,160 @@
         </is>
       </c>
     </row>
+    <row r="514">
+      <c r="A514" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-31 22:19:26+00:00</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>-40.957489283109446,172.10050015859824</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>-40.956827743877945,172.1003006061774</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>-40.956130350668936,172.10032653506997</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>-40.9554667831889,172.10013965599603</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>-40.95474721015778,172.10030500382535</t>
+        </is>
+      </c>
+      <c r="G514" t="inlineStr">
+        <is>
+          <t>-40.954155194537165,172.0996679865934</t>
+        </is>
+      </c>
+      <c r="H514" t="inlineStr">
+        <is>
+          <t>-40.95348378696336,172.09953029586734</t>
+        </is>
+      </c>
+      <c r="I514" t="inlineStr">
+        <is>
+          <t>-40.95281376378998,172.09934673987135</t>
+        </is>
+      </c>
+      <c r="J514" t="inlineStr">
+        <is>
+          <t>-40.95212983906458,172.0992224744221</t>
+        </is>
+      </c>
+      <c r="K514" t="inlineStr">
+        <is>
+          <t>-40.951451310309146,172.0990870423342</t>
+        </is>
+      </c>
+      <c r="L514" t="inlineStr">
+        <is>
+          <t>-40.95077452614189,172.09902022094147</t>
+        </is>
+      </c>
+      <c r="M514" t="inlineStr">
+        <is>
+          <t>-40.95009316771009,172.09901416735732</t>
+        </is>
+      </c>
+      <c r="N514" t="inlineStr">
+        <is>
+          <t>-40.94942134593274,172.09888113808546</t>
+        </is>
+      </c>
+      <c r="O514" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-08 22:19:13+00:00</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>-40.95751538756359,172.100335957545</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>-40.95684416075908,172.1001973419434</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>-40.956176495436026,172.100036281842</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>-40.955507880656604,172.09988115175994</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>-40.95479890148886,172.09997987125226</t>
+        </is>
+      </c>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>-40.95415173742952,172.0996897316847</t>
+        </is>
+      </c>
+      <c r="H515" t="inlineStr">
+        <is>
+          <t>-40.95347875845897,172.09956192477406</t>
+        </is>
+      </c>
+      <c r="I515" t="inlineStr">
+        <is>
+          <t>-40.9528116790323,172.09936157616897</t>
+        </is>
+      </c>
+      <c r="J515" t="inlineStr">
+        <is>
+          <t>-40.95213100029763,172.09921069260554</t>
+        </is>
+      </c>
+      <c r="K515" t="inlineStr">
+        <is>
+          <t>-40.95145318525016,172.09906209604915</t>
+        </is>
+      </c>
+      <c r="L515" t="inlineStr">
+        <is>
+          <t>-40.95077618781511,172.09899811237403</t>
+        </is>
+      </c>
+      <c r="M515" t="inlineStr">
+        <is>
+          <t>-40.95009538920681,172.09898461075383</t>
+        </is>
+      </c>
+      <c r="N515" t="inlineStr">
+        <is>
+          <t>-40.94942334525921,172.0988545374099</t>
+        </is>
+      </c>
+      <c r="O515" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0329/nzd0329.xlsx
+++ b/data/nzd0329/nzd0329.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O515"/>
+  <dimension ref="A1:O517"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26544,7 +26544,7 @@
         <v>398.15</v>
       </c>
       <c r="F515" t="n">
-        <v>373.27</v>
+        <v>372.59</v>
       </c>
       <c r="G515" t="n">
         <v>381.83</v>
@@ -26573,6 +26573,108 @@
       <c r="O515" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:19:11+00:00</t>
+        </is>
+      </c>
+      <c r="B516" t="n">
+        <v>402.9</v>
+      </c>
+      <c r="C516" t="n">
+        <v>400.03</v>
+      </c>
+      <c r="D516" t="n">
+        <v>397.89</v>
+      </c>
+      <c r="E516" t="n">
+        <v>394.47</v>
+      </c>
+      <c r="F516" t="n">
+        <v>387.9</v>
+      </c>
+      <c r="G516" t="n">
+        <v>381.78</v>
+      </c>
+      <c r="H516" t="n">
+        <v>375.43</v>
+      </c>
+      <c r="I516" t="n">
+        <v>375.94</v>
+      </c>
+      <c r="J516" t="n">
+        <v>376.71</v>
+      </c>
+      <c r="K516" t="n">
+        <v>383.1</v>
+      </c>
+      <c r="L516" t="n">
+        <v>381.87</v>
+      </c>
+      <c r="M516" t="n">
+        <v>375.68</v>
+      </c>
+      <c r="N516" t="n">
+        <v>377.96</v>
+      </c>
+      <c r="O516" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:13:01+00:00</t>
+        </is>
+      </c>
+      <c r="B517" t="n">
+        <v>403.45</v>
+      </c>
+      <c r="C517" t="n">
+        <v>400.34</v>
+      </c>
+      <c r="D517" t="n">
+        <v>398.16</v>
+      </c>
+      <c r="E517" t="n">
+        <v>394.74</v>
+      </c>
+      <c r="F517" t="n">
+        <v>388.02</v>
+      </c>
+      <c r="G517" t="n">
+        <v>382.48</v>
+      </c>
+      <c r="H517" t="n">
+        <v>376.1</v>
+      </c>
+      <c r="I517" t="n">
+        <v>376.17</v>
+      </c>
+      <c r="J517" t="n">
+        <v>377.2</v>
+      </c>
+      <c r="K517" t="n">
+        <v>384.96</v>
+      </c>
+      <c r="L517" t="n">
+        <v>384.43</v>
+      </c>
+      <c r="M517" t="n">
+        <v>378.3</v>
+      </c>
+      <c r="N517" t="n">
+        <v>381.47</v>
+      </c>
+      <c r="O517" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -26587,7 +26689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B539"/>
+  <dimension ref="A1:B541"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31980,6 +32082,26 @@
       </c>
       <c r="B539" t="n">
         <v>-0.72</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B540" t="n">
+        <v>-0.9</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B541" t="n">
+        <v>-0.05</v>
       </c>
     </row>
   </sheetData>
@@ -32148,28 +32270,28 @@
         <v>0.06519999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.414491776411109</v>
+        <v>-1.412270273900665</v>
       </c>
       <c r="J2" t="n">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="K2" t="n">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5297548929566195</v>
+        <v>0.5307890630032291</v>
       </c>
       <c r="M2" t="n">
-        <v>8.006950597554813</v>
+        <v>7.983428979434672</v>
       </c>
       <c r="N2" t="n">
-        <v>107.4095398788242</v>
+        <v>107.03171993297</v>
       </c>
       <c r="O2" t="n">
-        <v>10.36385738414149</v>
+        <v>10.34561356000551</v>
       </c>
       <c r="P2" t="n">
-        <v>437.5406155146625</v>
+        <v>437.5182266434539</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -32226,28 +32348,28 @@
         <v>0.0912</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.430632528892325</v>
+        <v>-1.418429430931041</v>
       </c>
       <c r="J3" t="n">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="K3" t="n">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4017035214776845</v>
+        <v>0.397892673002346</v>
       </c>
       <c r="M3" t="n">
-        <v>10.45490331844135</v>
+        <v>10.4747725291094</v>
       </c>
       <c r="N3" t="n">
-        <v>185.4393454753076</v>
+        <v>185.905464315249</v>
       </c>
       <c r="O3" t="n">
-        <v>13.61761159217385</v>
+        <v>13.63471541013046</v>
       </c>
       <c r="P3" t="n">
-        <v>420.5790499549053</v>
+        <v>420.4566552666285</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32304,28 +32426,28 @@
         <v>0.081</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.680352237643689</v>
+        <v>-1.653386616326767</v>
       </c>
       <c r="J4" t="n">
+        <v>516</v>
+      </c>
+      <c r="K4" t="n">
         <v>514</v>
       </c>
-      <c r="K4" t="n">
-        <v>512</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.1083034791317263</v>
+        <v>0.1055507396006379</v>
       </c>
       <c r="M4" t="n">
-        <v>29.93934708981162</v>
+        <v>29.94987495114279</v>
       </c>
       <c r="N4" t="n">
-        <v>1418.516067876993</v>
+        <v>1418.80901251297</v>
       </c>
       <c r="O4" t="n">
-        <v>37.66319248121424</v>
+        <v>37.66708128476335</v>
       </c>
       <c r="P4" t="n">
-        <v>403.7623409208229</v>
+        <v>403.4921568611607</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32382,28 +32504,28 @@
         <v>0.06569999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.404767662020911</v>
+        <v>-2.370567287932993</v>
       </c>
       <c r="J5" t="n">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="K5" t="n">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2084504355969674</v>
+        <v>0.2038914703959243</v>
       </c>
       <c r="M5" t="n">
-        <v>28.96509489161581</v>
+        <v>29.00454509501937</v>
       </c>
       <c r="N5" t="n">
-        <v>1305.303097812725</v>
+        <v>1309.175257048518</v>
       </c>
       <c r="O5" t="n">
-        <v>36.12897864336502</v>
+        <v>36.18252695775293</v>
       </c>
       <c r="P5" t="n">
-        <v>410.344001785999</v>
+        <v>409.9936052262888</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32460,28 +32582,28 @@
         <v>0.0479</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8824715120398344</v>
+        <v>-0.8755256434841246</v>
       </c>
       <c r="J6" t="n">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="K6" t="n">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="L6" t="n">
-        <v>0.066271949909952</v>
+        <v>0.06573170017162422</v>
       </c>
       <c r="M6" t="n">
-        <v>15.8937205494129</v>
+        <v>15.84894894667647</v>
       </c>
       <c r="N6" t="n">
-        <v>652.5785522484844</v>
+        <v>650.3822349869614</v>
       </c>
       <c r="O6" t="n">
-        <v>25.54561708490293</v>
+        <v>25.50259271107472</v>
       </c>
       <c r="P6" t="n">
-        <v>401.3261759644096</v>
+        <v>401.2547154778174</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32538,28 +32660,28 @@
         <v>0.0721</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.7389891040225955</v>
+        <v>-0.7385110305540832</v>
       </c>
       <c r="J7" t="n">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="K7" t="n">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1379825255388661</v>
+        <v>0.1387386778992749</v>
       </c>
       <c r="M7" t="n">
-        <v>8.433464613591648</v>
+        <v>8.403005396896608</v>
       </c>
       <c r="N7" t="n">
-        <v>206.7362769566301</v>
+        <v>205.9263007551415</v>
       </c>
       <c r="O7" t="n">
-        <v>14.37832663965561</v>
+        <v>14.35013242988167</v>
       </c>
       <c r="P7" t="n">
-        <v>401.0671700799081</v>
+        <v>401.0623396626213</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -32616,28 +32738,28 @@
         <v>0.0625</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.8832355365598811</v>
+        <v>-0.8832960856737877</v>
       </c>
       <c r="J8" t="n">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="K8" t="n">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3390586134043804</v>
+        <v>0.3408110867958319</v>
       </c>
       <c r="M8" t="n">
-        <v>6.939542764779969</v>
+        <v>6.91374352668316</v>
       </c>
       <c r="N8" t="n">
-        <v>91.32133368392169</v>
+        <v>90.96372404157884</v>
       </c>
       <c r="O8" t="n">
-        <v>9.556219633512077</v>
+        <v>9.537490447784409</v>
       </c>
       <c r="P8" t="n">
-        <v>399.2997346590754</v>
+        <v>399.3003466069832</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -32694,28 +32816,28 @@
         <v>0.1418</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.9577580758980658</v>
+        <v>-0.9525017777961646</v>
       </c>
       <c r="J9" t="n">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="K9" t="n">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4268739963281787</v>
+        <v>0.4253406802271041</v>
       </c>
       <c r="M9" t="n">
-        <v>6.128732887835938</v>
+        <v>6.132865522350819</v>
       </c>
       <c r="N9" t="n">
-        <v>74.29997564751309</v>
+        <v>74.22712214476491</v>
       </c>
       <c r="O9" t="n">
-        <v>8.619743363204794</v>
+        <v>8.615516359729398</v>
       </c>
       <c r="P9" t="n">
-        <v>393.9777590695945</v>
+        <v>393.924612630003</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -32772,28 +32894,28 @@
         <v>0.1123</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.8750277927882016</v>
+        <v>-0.8693648329246448</v>
       </c>
       <c r="J10" t="n">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="K10" t="n">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4097730481325257</v>
+        <v>0.4075693838225906</v>
       </c>
       <c r="M10" t="n">
-        <v>6.101617802579074</v>
+        <v>6.1071637964501</v>
       </c>
       <c r="N10" t="n">
-        <v>66.53435543487245</v>
+        <v>66.52694461497032</v>
       </c>
       <c r="O10" t="n">
-        <v>8.156859410022491</v>
+        <v>8.156405128178118</v>
       </c>
       <c r="P10" t="n">
-        <v>392.1042770857853</v>
+        <v>392.0470179234551</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -32850,28 +32972,28 @@
         <v>0.0985</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.9113455485687177</v>
+        <v>-0.9077820611457488</v>
       </c>
       <c r="J11" t="n">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="K11" t="n">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3053016301149624</v>
+        <v>0.3050734663913285</v>
       </c>
       <c r="M11" t="n">
-        <v>8.252297022212604</v>
+        <v>8.237322999712891</v>
       </c>
       <c r="N11" t="n">
-        <v>114.0144567515605</v>
+        <v>113.6724315193758</v>
       </c>
       <c r="O11" t="n">
-        <v>10.67775522998914</v>
+        <v>10.6617274172329</v>
       </c>
       <c r="P11" t="n">
-        <v>403.1427878787277</v>
+        <v>403.1067502704786</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -32928,28 +33050,28 @@
         <v>0.1001</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.009582936911454</v>
+        <v>-1.008884518627034</v>
       </c>
       <c r="J12" t="n">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="K12" t="n">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2971509980079566</v>
+        <v>0.2984592746897212</v>
       </c>
       <c r="M12" t="n">
-        <v>9.563246681902427</v>
+        <v>9.530447360880093</v>
       </c>
       <c r="N12" t="n">
-        <v>144.8711953936578</v>
+        <v>144.3134908216288</v>
       </c>
       <c r="O12" t="n">
-        <v>12.03624507035553</v>
+        <v>12.01305501617423</v>
       </c>
       <c r="P12" t="n">
-        <v>408.9642331645847</v>
+        <v>408.9571412969647</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -33006,28 +33128,28 @@
         <v>0.137</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.7657516345549075</v>
+        <v>-0.7653995590862815</v>
       </c>
       <c r="J13" t="n">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="K13" t="n">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2141710183429203</v>
+        <v>0.2152991650160229</v>
       </c>
       <c r="M13" t="n">
-        <v>8.74924731258862</v>
+        <v>8.719769580902724</v>
       </c>
       <c r="N13" t="n">
-        <v>129.0298843961183</v>
+        <v>128.5307956867178</v>
       </c>
       <c r="O13" t="n">
-        <v>11.35913220259885</v>
+        <v>11.33714230689188</v>
       </c>
       <c r="P13" t="n">
-        <v>396.8231040614628</v>
+        <v>396.8195106667145</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -33084,28 +33206,28 @@
         <v>0.1005</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.9111261466392545</v>
+        <v>-0.9077396863190194</v>
       </c>
       <c r="J14" t="n">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="K14" t="n">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="L14" t="n">
-        <v>0.3152659201614775</v>
+        <v>0.3151079000194832</v>
       </c>
       <c r="M14" t="n">
-        <v>8.106921717804227</v>
+        <v>8.091080228778658</v>
       </c>
       <c r="N14" t="n">
-        <v>108.7926264590571</v>
+        <v>108.4677018496218</v>
       </c>
       <c r="O14" t="n">
-        <v>10.43037038935134</v>
+        <v>10.41478285177477</v>
       </c>
       <c r="P14" t="n">
-        <v>399.0849540812324</v>
+        <v>399.0506412964206</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -33143,7 +33265,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O515"/>
+  <dimension ref="A1:O517"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72460,7 +72582,7 @@
       </c>
       <c r="F515" t="inlineStr">
         <is>
-          <t>-40.95479890148886,172.09997987125226</t>
+          <t>-40.95479764434297,172.09998777863112</t>
         </is>
       </c>
       <c r="G515" t="inlineStr">
@@ -72506,6 +72628,160 @@
       <c r="O515" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:19:11+00:00</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>-40.95750557068953,172.10039770738922</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>-40.956837301915776,172.10024048500213</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>-40.956170376120184,172.1000747729777</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>-40.95550107733741,172.09992394510525</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>-40.9548259484807,172.09980974625154</t>
+        </is>
+      </c>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>-40.954151644993445,172.09969031310422</t>
+        </is>
+      </c>
+      <c r="H516" t="inlineStr">
+        <is>
+          <t>-40.953476909741916,172.0995735530474</t>
+        </is>
+      </c>
+      <c r="I516" t="inlineStr">
+        <is>
+          <t>-40.95280967634988,172.09937582835957</t>
+        </is>
+      </c>
+      <c r="J516" t="inlineStr">
+        <is>
+          <t>-40.9521305125799,172.09921564096854</t>
+        </is>
+      </c>
+      <c r="K516" t="inlineStr">
+        <is>
+          <t>-40.95145451814333,172.0990443617225</t>
+        </is>
+      </c>
+      <c r="L516" t="inlineStr">
+        <is>
+          <t>-40.950778746961255,172.0989640628136</t>
+        </is>
+      </c>
+      <c r="M516" t="inlineStr">
+        <is>
+          <t>-40.95009856149093,172.0989424039209</t>
+        </is>
+      </c>
+      <c r="N516" t="inlineStr">
+        <is>
+          <t>-40.94942589550228,172.0988206067682</t>
+        </is>
+      </c>
+      <c r="O516" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:13:01+00:00</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>-40.957506587504774,172.10039131145513</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>-40.95683787502729,172.10023688005685</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>-40.95617087527936,172.10007163321762</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>-40.95550157649453,172.0999208053764</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>-40.95482617032786,172.0998083508306</t>
+        </is>
+      </c>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>-40.95415293909842,172.09968217323075</t>
+        </is>
+      </c>
+      <c r="H517" t="inlineStr">
+        <is>
+          <t>-40.95347814838248,172.09956576210433</t>
+        </is>
+      </c>
+      <c r="I517" t="inlineStr">
+        <is>
+          <t>-40.9528100539049,172.09937314147123</t>
+        </is>
+      </c>
+      <c r="J517" t="inlineStr">
+        <is>
+          <t>-40.95213108158391,172.09920986787836</t>
+        </is>
+      </c>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>-40.95145617092707,172.0990223711565</t>
+        </is>
+      </c>
+      <c r="L517" t="inlineStr">
+        <is>
+          <t>-40.95078102174937,172.0989337965356</t>
+        </is>
+      </c>
+      <c r="M517" t="inlineStr">
+        <is>
+          <t>-40.95010088959996,172.0989114285957</t>
+        </is>
+      </c>
+      <c r="N517" t="inlineStr">
+        <is>
+          <t>-40.94942901442704,172.09877910970832</t>
+        </is>
+      </c>
+      <c r="O517" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>

--- a/data/nzd0329/nzd0329.xlsx
+++ b/data/nzd0329/nzd0329.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O517"/>
+  <dimension ref="A1:O521"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26678,6 +26678,210 @@
         </is>
       </c>
     </row>
+    <row r="518">
+      <c r="A518" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:13:10+00:00</t>
+        </is>
+      </c>
+      <c r="B518" t="n">
+        <v>404.62</v>
+      </c>
+      <c r="C518" t="n">
+        <v>400.67</v>
+      </c>
+      <c r="D518" t="n">
+        <v>398.03</v>
+      </c>
+      <c r="E518" t="n">
+        <v>395.42</v>
+      </c>
+      <c r="F518" t="n">
+        <v>388.91</v>
+      </c>
+      <c r="G518" t="n">
+        <v>383.4</v>
+      </c>
+      <c r="H518" t="n">
+        <v>376.85</v>
+      </c>
+      <c r="I518" t="n">
+        <v>376.94</v>
+      </c>
+      <c r="J518" t="n">
+        <v>379.25</v>
+      </c>
+      <c r="K518" t="n">
+        <v>388.21</v>
+      </c>
+      <c r="L518" t="n">
+        <v>389.27</v>
+      </c>
+      <c r="M518" t="n">
+        <v>383.91</v>
+      </c>
+      <c r="N518" t="n">
+        <v>384.71</v>
+      </c>
+      <c r="O518" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-05 22:19:02+00:00</t>
+        </is>
+      </c>
+      <c r="B519" t="n">
+        <v>409.8</v>
+      </c>
+      <c r="C519" t="n">
+        <v>402.09</v>
+      </c>
+      <c r="D519" t="n">
+        <v>397.95</v>
+      </c>
+      <c r="E519" t="n">
+        <v>396.58</v>
+      </c>
+      <c r="F519" t="n">
+        <v>390.53</v>
+      </c>
+      <c r="G519" t="n">
+        <v>385.72</v>
+      </c>
+      <c r="H519" t="n">
+        <v>378.84</v>
+      </c>
+      <c r="I519" t="n">
+        <v>376.5</v>
+      </c>
+      <c r="J519" t="n">
+        <v>384.43</v>
+      </c>
+      <c r="K519" t="n">
+        <v>393.1</v>
+      </c>
+      <c r="L519" t="n">
+        <v>397.82</v>
+      </c>
+      <c r="M519" t="n">
+        <v>392.51</v>
+      </c>
+      <c r="N519" t="n">
+        <v>389.24</v>
+      </c>
+      <c r="O519" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:12:47+00:00</t>
+        </is>
+      </c>
+      <c r="B520" t="n">
+        <v>409.91</v>
+      </c>
+      <c r="C520" t="n">
+        <v>402.93</v>
+      </c>
+      <c r="D520" t="n">
+        <v>396.97</v>
+      </c>
+      <c r="E520" t="n">
+        <v>395.84</v>
+      </c>
+      <c r="F520" t="n">
+        <v>391.14</v>
+      </c>
+      <c r="G520" t="n">
+        <v>384.6</v>
+      </c>
+      <c r="H520" t="n">
+        <v>351.87</v>
+      </c>
+      <c r="I520" t="n">
+        <v>376.5</v>
+      </c>
+      <c r="J520" t="n">
+        <v>384.43</v>
+      </c>
+      <c r="K520" t="n">
+        <v>393.1</v>
+      </c>
+      <c r="L520" t="n">
+        <v>397.82</v>
+      </c>
+      <c r="M520" t="n">
+        <v>392.51</v>
+      </c>
+      <c r="N520" t="n">
+        <v>389.24</v>
+      </c>
+      <c r="O520" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:18:57+00:00</t>
+        </is>
+      </c>
+      <c r="B521" t="n">
+        <v>409.19</v>
+      </c>
+      <c r="C521" t="n">
+        <v>404.01</v>
+      </c>
+      <c r="D521" t="n">
+        <v>398.28</v>
+      </c>
+      <c r="E521" t="n">
+        <v>396</v>
+      </c>
+      <c r="F521" t="n">
+        <v>390.63</v>
+      </c>
+      <c r="G521" t="n">
+        <v>383.12</v>
+      </c>
+      <c r="H521" t="n">
+        <v>326.3</v>
+      </c>
+      <c r="I521" t="n">
+        <v>376.5</v>
+      </c>
+      <c r="J521" t="n">
+        <v>384.43</v>
+      </c>
+      <c r="K521" t="n">
+        <v>393.1</v>
+      </c>
+      <c r="L521" t="n">
+        <v>397.82</v>
+      </c>
+      <c r="M521" t="n">
+        <v>392.51</v>
+      </c>
+      <c r="N521" t="n">
+        <v>389.24</v>
+      </c>
+      <c r="O521" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -26689,7 +26893,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B541"/>
+  <dimension ref="A1:B545"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32102,6 +32306,46 @@
       </c>
       <c r="B541" t="n">
         <v>-0.05</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B542" t="n">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>2026-04-05 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B543" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B544" t="n">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B545" t="n">
+        <v>-0.3</v>
       </c>
     </row>
   </sheetData>
@@ -32270,28 +32514,28 @@
         <v>0.06519999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.412270273900665</v>
+        <v>-1.400597844454083</v>
       </c>
       <c r="J2" t="n">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="K2" t="n">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5307890630032291</v>
+        <v>0.5290912738400876</v>
       </c>
       <c r="M2" t="n">
-        <v>7.983428979434672</v>
+        <v>7.961033404461123</v>
       </c>
       <c r="N2" t="n">
-        <v>107.03171993297</v>
+        <v>106.7871679252504</v>
       </c>
       <c r="O2" t="n">
-        <v>10.34561356000551</v>
+        <v>10.33378768531899</v>
       </c>
       <c r="P2" t="n">
-        <v>437.5182266434539</v>
+        <v>437.4000109982087</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -32348,28 +32592,28 @@
         <v>0.0912</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.418429430931041</v>
+        <v>-1.391397892745554</v>
       </c>
       <c r="J3" t="n">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="K3" t="n">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="L3" t="n">
-        <v>0.397892673002346</v>
+        <v>0.3885565240567077</v>
       </c>
       <c r="M3" t="n">
-        <v>10.4747725291094</v>
+        <v>10.53010670503628</v>
       </c>
       <c r="N3" t="n">
-        <v>185.905464315249</v>
+        <v>187.4219625164261</v>
       </c>
       <c r="O3" t="n">
-        <v>13.63471541013046</v>
+        <v>13.6902141150687</v>
       </c>
       <c r="P3" t="n">
-        <v>420.4566552666285</v>
+        <v>420.184234980757</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32426,28 +32670,28 @@
         <v>0.081</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.653386616326767</v>
+        <v>-1.600927198894211</v>
       </c>
       <c r="J4" t="n">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="K4" t="n">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1055507396006379</v>
+        <v>0.1002736160741734</v>
       </c>
       <c r="M4" t="n">
-        <v>29.94987495114279</v>
+        <v>29.96606443518472</v>
       </c>
       <c r="N4" t="n">
-        <v>1418.80901251297</v>
+        <v>1418.961432211369</v>
       </c>
       <c r="O4" t="n">
-        <v>37.66708128476335</v>
+        <v>37.66910447848966</v>
       </c>
       <c r="P4" t="n">
-        <v>403.4921568611607</v>
+        <v>402.964051594377</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32504,28 +32748,28 @@
         <v>0.06569999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.370567287932993</v>
+        <v>-2.301725165411078</v>
       </c>
       <c r="J5" t="n">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="K5" t="n">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2038914703959243</v>
+        <v>0.1946806559509255</v>
       </c>
       <c r="M5" t="n">
-        <v>29.00454509501937</v>
+        <v>29.08804513538201</v>
       </c>
       <c r="N5" t="n">
-        <v>1309.175257048518</v>
+        <v>1317.383446315033</v>
       </c>
       <c r="O5" t="n">
-        <v>36.18252695775293</v>
+        <v>36.29577725183789</v>
       </c>
       <c r="P5" t="n">
-        <v>409.9936052262888</v>
+        <v>409.2850100954207</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32582,28 +32826,28 @@
         <v>0.0479</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8755256434841246</v>
+        <v>-0.8580968376761509</v>
       </c>
       <c r="J6" t="n">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="K6" t="n">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="L6" t="n">
-        <v>0.06573170017162422</v>
+        <v>0.0641048362881983</v>
       </c>
       <c r="M6" t="n">
-        <v>15.84894894667647</v>
+        <v>15.7637155903206</v>
       </c>
       <c r="N6" t="n">
-        <v>650.3822349869614</v>
+        <v>646.4136806157901</v>
       </c>
       <c r="O6" t="n">
-        <v>25.50259271107472</v>
+        <v>25.42466677492136</v>
       </c>
       <c r="P6" t="n">
-        <v>401.2547154778174</v>
+        <v>401.0745651995338</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32660,28 +32904,28 @@
         <v>0.0721</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.7385110305540832</v>
+        <v>-0.7346143937804616</v>
       </c>
       <c r="J7" t="n">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="K7" t="n">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1387386778992749</v>
+        <v>0.1392515383510698</v>
       </c>
       <c r="M7" t="n">
-        <v>8.403005396896608</v>
+        <v>8.358981768011811</v>
       </c>
       <c r="N7" t="n">
-        <v>205.9263007551415</v>
+        <v>204.3896600014645</v>
       </c>
       <c r="O7" t="n">
-        <v>14.35013242988167</v>
+        <v>14.29649117795917</v>
       </c>
       <c r="P7" t="n">
-        <v>401.0623396626213</v>
+        <v>401.0228080271548</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -32738,28 +32982,28 @@
         <v>0.0625</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.8832960856737877</v>
+        <v>-0.9073828190922609</v>
       </c>
       <c r="J8" t="n">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="K8" t="n">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3408110867958319</v>
+        <v>0.3422649573183423</v>
       </c>
       <c r="M8" t="n">
-        <v>6.91374352668316</v>
+        <v>7.026582793270487</v>
       </c>
       <c r="N8" t="n">
-        <v>90.96372404157884</v>
+        <v>96.08718116911821</v>
       </c>
       <c r="O8" t="n">
-        <v>9.537490447784409</v>
+        <v>9.802406906934552</v>
       </c>
       <c r="P8" t="n">
-        <v>399.3003466069832</v>
+        <v>399.5465225296112</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -32816,28 +33060,28 @@
         <v>0.1418</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.9525017777961646</v>
+        <v>-0.9413735209519959</v>
       </c>
       <c r="J9" t="n">
+        <v>520</v>
+      </c>
+      <c r="K9" t="n">
         <v>516</v>
       </c>
-      <c r="K9" t="n">
-        <v>512</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.4253406802271041</v>
+        <v>0.4216985025087802</v>
       </c>
       <c r="M9" t="n">
-        <v>6.132865522350819</v>
+        <v>6.143844352656472</v>
       </c>
       <c r="N9" t="n">
-        <v>74.22712214476491</v>
+        <v>74.14380698162111</v>
       </c>
       <c r="O9" t="n">
-        <v>8.615516359729398</v>
+        <v>8.610679821107107</v>
       </c>
       <c r="P9" t="n">
-        <v>393.924612630003</v>
+        <v>393.811573173791</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -32894,28 +33138,28 @@
         <v>0.1123</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.8693648329246448</v>
+        <v>-0.8496764385547558</v>
       </c>
       <c r="J10" t="n">
+        <v>520</v>
+      </c>
+      <c r="K10" t="n">
         <v>516</v>
       </c>
-      <c r="K10" t="n">
-        <v>512</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.4075693838225906</v>
+        <v>0.3945523336220651</v>
       </c>
       <c r="M10" t="n">
-        <v>6.1071637964501</v>
+        <v>6.160703953245362</v>
       </c>
       <c r="N10" t="n">
-        <v>66.52694461497032</v>
+        <v>67.58927858692167</v>
       </c>
       <c r="O10" t="n">
-        <v>8.156405128178118</v>
+        <v>8.221269888947916</v>
       </c>
       <c r="P10" t="n">
-        <v>392.0470179234551</v>
+        <v>391.8469752668742</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -32972,28 +33216,28 @@
         <v>0.0985</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.9077820611457488</v>
+        <v>-0.8898819948642802</v>
       </c>
       <c r="J11" t="n">
+        <v>520</v>
+      </c>
+      <c r="K11" t="n">
         <v>516</v>
       </c>
-      <c r="K11" t="n">
-        <v>512</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.3050734663913285</v>
+        <v>0.2974729211295135</v>
       </c>
       <c r="M11" t="n">
-        <v>8.237322999712891</v>
+        <v>8.260036479551157</v>
       </c>
       <c r="N11" t="n">
-        <v>113.6724315193758</v>
+        <v>114.0982903218127</v>
       </c>
       <c r="O11" t="n">
-        <v>10.6617274172329</v>
+        <v>10.68168012635712</v>
       </c>
       <c r="P11" t="n">
-        <v>403.1067502704786</v>
+        <v>402.9248761576641</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -33050,28 +33294,28 @@
         <v>0.1001</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.008884518627034</v>
+        <v>-0.9899597455040805</v>
       </c>
       <c r="J12" t="n">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="K12" t="n">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2984592746897212</v>
+        <v>0.2915817752942977</v>
       </c>
       <c r="M12" t="n">
-        <v>9.530447360880093</v>
+        <v>9.549949062057946</v>
       </c>
       <c r="N12" t="n">
-        <v>144.3134908216288</v>
+        <v>144.7056067948291</v>
       </c>
       <c r="O12" t="n">
-        <v>12.01305501617423</v>
+        <v>12.02936435539422</v>
       </c>
       <c r="P12" t="n">
-        <v>408.9571412969647</v>
+        <v>408.7643030845132</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -33128,28 +33372,28 @@
         <v>0.137</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.7653995590862815</v>
+        <v>-0.7460301157763396</v>
       </c>
       <c r="J13" t="n">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="K13" t="n">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2152991650160229</v>
+        <v>0.2072370190394285</v>
       </c>
       <c r="M13" t="n">
-        <v>8.719769580902724</v>
+        <v>8.742088581115162</v>
       </c>
       <c r="N13" t="n">
-        <v>128.5307956867178</v>
+        <v>129.116384543369</v>
       </c>
       <c r="O13" t="n">
-        <v>11.33714230689188</v>
+        <v>11.36293908033344</v>
       </c>
       <c r="P13" t="n">
-        <v>396.8195106667145</v>
+        <v>396.6214417867162</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -33206,28 +33450,28 @@
         <v>0.1005</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.9077396863190194</v>
+        <v>-0.8894098681488832</v>
       </c>
       <c r="J14" t="n">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="K14" t="n">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="L14" t="n">
-        <v>0.3151079000194832</v>
+        <v>0.306927301299518</v>
       </c>
       <c r="M14" t="n">
-        <v>8.091080228778658</v>
+        <v>8.114065014634589</v>
       </c>
       <c r="N14" t="n">
-        <v>108.4677018496218</v>
+        <v>108.9874681303926</v>
       </c>
       <c r="O14" t="n">
-        <v>10.41478285177477</v>
+        <v>10.4397063239534</v>
       </c>
       <c r="P14" t="n">
-        <v>399.0506412964206</v>
+        <v>398.8640843436702</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -33265,7 +33509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O517"/>
+  <dimension ref="A1:O521"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72785,6 +73029,314 @@
         </is>
       </c>
     </row>
+    <row r="518">
+      <c r="A518" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:13:10+00:00</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>-40.95750875054692,172.1003777055584</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>-40.95683848511363,172.1002330425344</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>-40.956170634943476,172.10007314495397</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>-40.955502833630575,172.09991289791097</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>-40.95482781569365,172.09979800145842</t>
+        </is>
+      </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>-40.95415463992124,172.09967147511085</t>
+        </is>
+      </c>
+      <c r="H518" t="inlineStr">
+        <is>
+          <t>-40.95347953491977,172.09955704089904</t>
+        </is>
+      </c>
+      <c r="I518" t="inlineStr">
+        <is>
+          <t>-40.952811317892966,172.09936414623618</t>
+        </is>
+      </c>
+      <c r="J518" t="inlineStr">
+        <is>
+          <t>-40.95213346210773,172.0991857151531</t>
+        </is>
+      </c>
+      <c r="K518" t="inlineStr">
+        <is>
+          <t>-40.95145905884552,172.09898394677802</t>
+        </is>
+      </c>
+      <c r="L518" t="inlineStr">
+        <is>
+          <t>-40.95078532249889,172.09887657434845</t>
+        </is>
+      </c>
+      <c r="M518" t="inlineStr">
+        <is>
+          <t>-40.95010587456871,172.09884510356056</t>
+        </is>
+      </c>
+      <c r="N518" t="inlineStr">
+        <is>
+          <t>-40.94943189342122,172.09874080472676</t>
+        </is>
+      </c>
+      <c r="O518" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-05 22:19:02+00:00</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>-40.95751832707307,172.1003174674752</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>-40.95684111033212,172.1002165295582</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>-40.95617048704446,172.10007407525325</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>-40.95550497815554,172.0998994087045</t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>-40.95483081062675,172.09977916327406</t>
+        </is>
+      </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>-40.95415892894827,172.09964449724097</t>
+        </is>
+      </c>
+      <c r="H519" t="inlineStr">
+        <is>
+          <t>-40.95348321386221,172.09953390063268</t>
+        </is>
+      </c>
+      <c r="I519" t="inlineStr">
+        <is>
+          <t>-40.95281059561416,172.09936928637055</t>
+        </is>
+      </c>
+      <c r="J519" t="inlineStr">
+        <is>
+          <t>-40.95213947726237,172.0991246853327</t>
+        </is>
+      </c>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>-40.951463404027876,172.09892613286115</t>
+        </is>
+      </c>
+      <c r="L519" t="inlineStr">
+        <is>
+          <t>-40.950792919827684,172.0987754896828</t>
+        </is>
+      </c>
+      <c r="M519" t="inlineStr">
+        <is>
+          <t>-40.95011351633598,172.09874342880056</t>
+        </is>
+      </c>
+      <c r="N519" t="inlineStr">
+        <is>
+          <t>-40.94943591866021,172.09868724868252</t>
+        </is>
+      </c>
+      <c r="O519" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:12:47+00:00</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>-40.957518530435244,172.10031618828793</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>-40.95684266327716,172.10020676131816</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>-40.95616867528085,172.10008547141902</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>-40.95550361009669,172.09990801388804</t>
+        </is>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>-40.954831938347674,172.09977206988322</t>
+        </is>
+      </c>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>-40.954156858384295,172.09965752104065</t>
+        </is>
+      </c>
+      <c r="H520" t="inlineStr">
+        <is>
+          <t>-40.95343335362679,172.09984751498575</t>
+        </is>
+      </c>
+      <c r="I520" t="inlineStr">
+        <is>
+          <t>-40.95281059561416,172.09936928637055</t>
+        </is>
+      </c>
+      <c r="J520" t="inlineStr">
+        <is>
+          <t>-40.95213947726237,172.0991246853327</t>
+        </is>
+      </c>
+      <c r="K520" t="inlineStr">
+        <is>
+          <t>-40.951463404027876,172.09892613286115</t>
+        </is>
+      </c>
+      <c r="L520" t="inlineStr">
+        <is>
+          <t>-40.950792919827684,172.0987754896828</t>
+        </is>
+      </c>
+      <c r="M520" t="inlineStr">
+        <is>
+          <t>-40.95011351633598,172.09874342880056</t>
+        </is>
+      </c>
+      <c r="N520" t="inlineStr">
+        <is>
+          <t>-40.94943591866021,172.09868724868252</t>
+        </is>
+      </c>
+      <c r="O520" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:18:57+00:00</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>-40.95751719933708,172.10032456115</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>-40.95684465991954,172.10019420215176</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>-40.95617109712786,172.10007023776873</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>-40.95550390589325,172.09990615330784</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>-40.95483099549906,172.0997780004231</t>
+        </is>
+      </c>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>-40.954154122279625,172.09967473106045</t>
+        </is>
+      </c>
+      <c r="H521" t="inlineStr">
+        <is>
+          <t>-40.953386080819925,172.10014484934325</t>
+        </is>
+      </c>
+      <c r="I521" t="inlineStr">
+        <is>
+          <t>-40.95281059561416,172.09936928637055</t>
+        </is>
+      </c>
+      <c r="J521" t="inlineStr">
+        <is>
+          <t>-40.95213947726237,172.0991246853327</t>
+        </is>
+      </c>
+      <c r="K521" t="inlineStr">
+        <is>
+          <t>-40.951463404027876,172.09892613286115</t>
+        </is>
+      </c>
+      <c r="L521" t="inlineStr">
+        <is>
+          <t>-40.950792919827684,172.0987754896828</t>
+        </is>
+      </c>
+      <c r="M521" t="inlineStr">
+        <is>
+          <t>-40.95011351633598,172.09874342880056</t>
+        </is>
+      </c>
+      <c r="N521" t="inlineStr">
+        <is>
+          <t>-40.94943591866021,172.09868724868252</t>
+        </is>
+      </c>
+      <c r="O521" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0329/nzd0329.xlsx
+++ b/data/nzd0329/nzd0329.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O521"/>
+  <dimension ref="A1:O524"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26882,6 +26882,159 @@
         </is>
       </c>
     </row>
+    <row r="522">
+      <c r="A522" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:12:32+00:00</t>
+        </is>
+      </c>
+      <c r="B522" t="n">
+        <v>408.7</v>
+      </c>
+      <c r="C522" t="n">
+        <v>404.88</v>
+      </c>
+      <c r="D522" t="n">
+        <v>398.5</v>
+      </c>
+      <c r="E522" t="n">
+        <v>396.01</v>
+      </c>
+      <c r="F522" t="n">
+        <v>390.52</v>
+      </c>
+      <c r="G522" t="n">
+        <v>383.12</v>
+      </c>
+      <c r="H522" t="n">
+        <v>303.99</v>
+      </c>
+      <c r="I522" t="n">
+        <v>376.5</v>
+      </c>
+      <c r="J522" t="n">
+        <v>384.43</v>
+      </c>
+      <c r="K522" t="n">
+        <v>393.1</v>
+      </c>
+      <c r="L522" t="n">
+        <v>397.82</v>
+      </c>
+      <c r="M522" t="n">
+        <v>392.51</v>
+      </c>
+      <c r="N522" t="n">
+        <v>389.24</v>
+      </c>
+      <c r="O522" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:18:41+00:00</t>
+        </is>
+      </c>
+      <c r="B523" t="n">
+        <v>408.84</v>
+      </c>
+      <c r="C523" t="n">
+        <v>404.11</v>
+      </c>
+      <c r="D523" t="n">
+        <v>387.63</v>
+      </c>
+      <c r="E523" t="n">
+        <v>384.96</v>
+      </c>
+      <c r="F523" t="n">
+        <v>390.52</v>
+      </c>
+      <c r="G523" t="n">
+        <v>383.12</v>
+      </c>
+      <c r="H523" t="n">
+        <v>303.99</v>
+      </c>
+      <c r="I523" t="n">
+        <v>376.5</v>
+      </c>
+      <c r="J523" t="n">
+        <v>384.43</v>
+      </c>
+      <c r="K523" t="n">
+        <v>393.1</v>
+      </c>
+      <c r="L523" t="n">
+        <v>397.82</v>
+      </c>
+      <c r="M523" t="n">
+        <v>392.51</v>
+      </c>
+      <c r="N523" t="n">
+        <v>389.24</v>
+      </c>
+      <c r="O523" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-23 22:18:30+00:00</t>
+        </is>
+      </c>
+      <c r="B524" t="n">
+        <v>408.24</v>
+      </c>
+      <c r="C524" t="n">
+        <v>403.41</v>
+      </c>
+      <c r="D524" t="n">
+        <v>385.03</v>
+      </c>
+      <c r="E524" t="n">
+        <v>381.67</v>
+      </c>
+      <c r="F524" t="n">
+        <v>387.62</v>
+      </c>
+      <c r="G524" t="n">
+        <v>379.75</v>
+      </c>
+      <c r="H524" t="n">
+        <v>303.99</v>
+      </c>
+      <c r="I524" t="n">
+        <v>373.79</v>
+      </c>
+      <c r="J524" t="n">
+        <v>382.34</v>
+      </c>
+      <c r="K524" t="n">
+        <v>392.33</v>
+      </c>
+      <c r="L524" t="n">
+        <v>398.74</v>
+      </c>
+      <c r="M524" t="n">
+        <v>393.52</v>
+      </c>
+      <c r="N524" t="n">
+        <v>388.39</v>
+      </c>
+      <c r="O524" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -26893,7 +27046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B545"/>
+  <dimension ref="A1:B548"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32346,6 +32499,36 @@
       </c>
       <c r="B545" t="n">
         <v>-0.3</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B546" t="n">
+        <v>-0.8</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B547" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>2026-05-23 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B548" t="n">
+        <v>-0.9399999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -32514,28 +32697,28 @@
         <v>0.06519999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.400597844454083</v>
+        <v>-1.391809855223474</v>
       </c>
       <c r="J2" t="n">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="K2" t="n">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5290912738400876</v>
+        <v>0.5277820817684782</v>
       </c>
       <c r="M2" t="n">
-        <v>7.961033404461123</v>
+        <v>7.944432085301695</v>
       </c>
       <c r="N2" t="n">
-        <v>106.7871679252504</v>
+        <v>106.5926427460222</v>
       </c>
       <c r="O2" t="n">
-        <v>10.33378768531899</v>
+        <v>10.32437130027888</v>
       </c>
       <c r="P2" t="n">
-        <v>437.4000109982087</v>
+        <v>437.3107092114827</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -32592,28 +32775,28 @@
         <v>0.0912</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.391397892745554</v>
+        <v>-1.369947966604256</v>
       </c>
       <c r="J3" t="n">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="K3" t="n">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3885565240567077</v>
+        <v>0.3806883899879494</v>
       </c>
       <c r="M3" t="n">
-        <v>10.53010670503628</v>
+        <v>10.57963896493509</v>
       </c>
       <c r="N3" t="n">
-        <v>187.4219625164261</v>
+        <v>188.8647487878771</v>
       </c>
       <c r="O3" t="n">
-        <v>13.6902141150687</v>
+        <v>13.74280716549123</v>
       </c>
       <c r="P3" t="n">
-        <v>420.184234980757</v>
+        <v>419.9672831242598</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32670,28 +32853,28 @@
         <v>0.081</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.600927198894211</v>
+        <v>-1.570292009044085</v>
       </c>
       <c r="J4" t="n">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="K4" t="n">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1002736160741734</v>
+        <v>0.09749376788443764</v>
       </c>
       <c r="M4" t="n">
-        <v>29.96606443518472</v>
+        <v>29.93651068777848</v>
       </c>
       <c r="N4" t="n">
-        <v>1418.961432211369</v>
+        <v>1416.144278466618</v>
       </c>
       <c r="O4" t="n">
-        <v>37.66910447848966</v>
+        <v>37.63169247411839</v>
       </c>
       <c r="P4" t="n">
-        <v>402.964051594377</v>
+        <v>402.6545674193258</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32748,28 +32931,28 @@
         <v>0.06569999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.301725165411078</v>
+        <v>-2.260388436384909</v>
       </c>
       <c r="J5" t="n">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="K5" t="n">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1946806559509255</v>
+        <v>0.1897176189213363</v>
       </c>
       <c r="M5" t="n">
-        <v>29.08804513538201</v>
+        <v>29.10761537262651</v>
       </c>
       <c r="N5" t="n">
-        <v>1317.383446315033</v>
+        <v>1318.974950949942</v>
       </c>
       <c r="O5" t="n">
-        <v>36.29577725183789</v>
+        <v>36.3176947361743</v>
       </c>
       <c r="P5" t="n">
-        <v>409.2850100954207</v>
+        <v>408.8580453808071</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32826,28 +33009,28 @@
         <v>0.0479</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8580968376761509</v>
+        <v>-0.84618338134426</v>
       </c>
       <c r="J6" t="n">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="K6" t="n">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0641048362881983</v>
+        <v>0.06304168967105972</v>
       </c>
       <c r="M6" t="n">
-        <v>15.7637155903206</v>
+        <v>15.69858504318312</v>
       </c>
       <c r="N6" t="n">
-        <v>646.4136806157901</v>
+        <v>643.3552427429711</v>
       </c>
       <c r="O6" t="n">
-        <v>25.42466677492136</v>
+        <v>25.36444840210351</v>
       </c>
       <c r="P6" t="n">
-        <v>401.0745651995338</v>
+        <v>400.9509970529014</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32904,28 +33087,28 @@
         <v>0.0721</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.7346143937804616</v>
+        <v>-0.7340052919125674</v>
       </c>
       <c r="J7" t="n">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="K7" t="n">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1392515383510698</v>
+        <v>0.1403958085233625</v>
       </c>
       <c r="M7" t="n">
-        <v>8.358981768011811</v>
+        <v>8.320026363991282</v>
       </c>
       <c r="N7" t="n">
-        <v>204.3896600014645</v>
+        <v>203.2176511021464</v>
       </c>
       <c r="O7" t="n">
-        <v>14.29649117795917</v>
+        <v>14.25544285885733</v>
       </c>
       <c r="P7" t="n">
-        <v>401.0228080271548</v>
+        <v>401.0166348854711</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -32982,28 +33165,28 @@
         <v>0.0625</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.9073828190922609</v>
+        <v>-0.9808550620249999</v>
       </c>
       <c r="J8" t="n">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="K8" t="n">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3422649573183423</v>
+        <v>0.320517044088991</v>
       </c>
       <c r="M8" t="n">
-        <v>7.026582793270487</v>
+        <v>7.478426124275944</v>
       </c>
       <c r="N8" t="n">
-        <v>96.08718116911821</v>
+        <v>124.5409540276965</v>
       </c>
       <c r="O8" t="n">
-        <v>9.802406906934552</v>
+        <v>11.15979184517778</v>
       </c>
       <c r="P8" t="n">
-        <v>399.5465225296112</v>
+        <v>400.2989742641237</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -33060,28 +33243,28 @@
         <v>0.1418</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.9413735209519959</v>
+        <v>-0.9342728871254823</v>
       </c>
       <c r="J9" t="n">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="K9" t="n">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4216985025087802</v>
+        <v>0.4198279708757948</v>
       </c>
       <c r="M9" t="n">
-        <v>6.143844352656472</v>
+        <v>6.145318237460524</v>
       </c>
       <c r="N9" t="n">
-        <v>74.14380698162111</v>
+        <v>73.99706488375642</v>
       </c>
       <c r="O9" t="n">
-        <v>8.610679821107107</v>
+        <v>8.602154665184557</v>
       </c>
       <c r="P9" t="n">
-        <v>393.811573173791</v>
+        <v>393.7391963987623</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -33138,28 +33321,28 @@
         <v>0.1123</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.8496764385547558</v>
+        <v>-0.8347267230091012</v>
       </c>
       <c r="J10" t="n">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="K10" t="n">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3945523336220651</v>
+        <v>0.3845358359009077</v>
       </c>
       <c r="M10" t="n">
-        <v>6.160703953245362</v>
+        <v>6.2020967356707</v>
       </c>
       <c r="N10" t="n">
-        <v>67.58927858692167</v>
+        <v>68.41261189445972</v>
       </c>
       <c r="O10" t="n">
-        <v>8.221269888947916</v>
+        <v>8.271191685268798</v>
       </c>
       <c r="P10" t="n">
-        <v>391.8469752668742</v>
+        <v>391.6945614891376</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -33216,28 +33399,28 @@
         <v>0.0985</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.8898819948642802</v>
+        <v>-0.8758453158398998</v>
       </c>
       <c r="J11" t="n">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="K11" t="n">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2974729211295135</v>
+        <v>0.2912691328614007</v>
       </c>
       <c r="M11" t="n">
-        <v>8.260036479551157</v>
+        <v>8.282959864727792</v>
       </c>
       <c r="N11" t="n">
-        <v>114.0982903218127</v>
+        <v>114.5046947761306</v>
       </c>
       <c r="O11" t="n">
-        <v>10.68168012635712</v>
+        <v>10.70068664974966</v>
       </c>
       <c r="P11" t="n">
-        <v>402.9248761576641</v>
+        <v>402.7817601794532</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -33294,28 +33477,28 @@
         <v>0.1001</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.9899597455040805</v>
+        <v>-0.9736446006900482</v>
       </c>
       <c r="J12" t="n">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="K12" t="n">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2915817752942977</v>
+        <v>0.2850653995206816</v>
       </c>
       <c r="M12" t="n">
-        <v>9.549949062057946</v>
+        <v>9.575235189269826</v>
       </c>
       <c r="N12" t="n">
-        <v>144.7056067948291</v>
+        <v>145.2925969924028</v>
       </c>
       <c r="O12" t="n">
-        <v>12.02936435539422</v>
+        <v>12.05373788467307</v>
       </c>
       <c r="P12" t="n">
-        <v>408.7643030845132</v>
+        <v>408.5974898639354</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -33372,28 +33555,28 @@
         <v>0.137</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.7460301157763396</v>
+        <v>-0.7293647844130703</v>
       </c>
       <c r="J13" t="n">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="K13" t="n">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2072370190394285</v>
+        <v>0.1998677182949983</v>
       </c>
       <c r="M13" t="n">
-        <v>8.742088581115162</v>
+        <v>8.768695590630337</v>
       </c>
       <c r="N13" t="n">
-        <v>129.116384543369</v>
+        <v>129.8587529381956</v>
       </c>
       <c r="O13" t="n">
-        <v>11.36293908033344</v>
+        <v>11.39555847416859</v>
       </c>
       <c r="P13" t="n">
-        <v>396.6214417867162</v>
+        <v>396.45044026592</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -33450,28 +33633,28 @@
         <v>0.1005</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.8894098681488832</v>
+        <v>-0.8751796308696761</v>
       </c>
       <c r="J14" t="n">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="K14" t="n">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="L14" t="n">
-        <v>0.306927301299518</v>
+        <v>0.3003604376979252</v>
       </c>
       <c r="M14" t="n">
-        <v>8.114065014634589</v>
+        <v>8.133756209495431</v>
       </c>
       <c r="N14" t="n">
-        <v>108.9874681303926</v>
+        <v>109.4506929817794</v>
       </c>
       <c r="O14" t="n">
-        <v>10.4397063239534</v>
+        <v>10.46186852248581</v>
       </c>
       <c r="P14" t="n">
-        <v>398.8640843436702</v>
+        <v>398.7187432726634</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -33509,7 +33692,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O521"/>
+  <dimension ref="A1:O524"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73337,6 +73520,237 @@
         </is>
       </c>
     </row>
+    <row r="522">
+      <c r="A522" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:12:32+00:00</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>-40.95751629345047,172.10033025934754</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>-40.95684626832492,172.10018408504493</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>-40.95617150385006,172.10006767944566</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>-40.95550392438054,172.09990603702158</t>
+        </is>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>-40.954830792139525,172.09977927955916</t>
+        </is>
+      </c>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>-40.954154122279625,172.09967473106045</t>
+        </is>
+      </c>
+      <c r="H522" t="inlineStr">
+        <is>
+          <t>-40.95334483434205,172.10040427526937</t>
+        </is>
+      </c>
+      <c r="I522" t="inlineStr">
+        <is>
+          <t>-40.95281059561416,172.09936928637055</t>
+        </is>
+      </c>
+      <c r="J522" t="inlineStr">
+        <is>
+          <t>-40.95213947726237,172.0991246853327</t>
+        </is>
+      </c>
+      <c r="K522" t="inlineStr">
+        <is>
+          <t>-40.951463404027876,172.09892613286115</t>
+        </is>
+      </c>
+      <c r="L522" t="inlineStr">
+        <is>
+          <t>-40.950792919827684,172.0987754896828</t>
+        </is>
+      </c>
+      <c r="M522" t="inlineStr">
+        <is>
+          <t>-40.95011351633598,172.09874342880056</t>
+        </is>
+      </c>
+      <c r="N522" t="inlineStr">
+        <is>
+          <t>-40.94943591866021,172.09868724868252</t>
+        </is>
+      </c>
+      <c r="O522" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:18:41+00:00</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>-40.957516552275244,172.10032863129112</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>-40.95684484479377,172.10019303926592</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>-40.95615140800764,172.1001940838258</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>-40.95548349585972,172.10003453330324</t>
+        </is>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>-40.954830792139525,172.09977927955916</t>
+        </is>
+      </c>
+      <c r="G523" t="inlineStr">
+        <is>
+          <t>-40.954154122279625,172.09967473106045</t>
+        </is>
+      </c>
+      <c r="H523" t="inlineStr">
+        <is>
+          <t>-40.95334483434205,172.10040427526937</t>
+        </is>
+      </c>
+      <c r="I523" t="inlineStr">
+        <is>
+          <t>-40.95281059561416,172.09936928637055</t>
+        </is>
+      </c>
+      <c r="J523" t="inlineStr">
+        <is>
+          <t>-40.95213947726237,172.0991246853327</t>
+        </is>
+      </c>
+      <c r="K523" t="inlineStr">
+        <is>
+          <t>-40.951463404027876,172.09892613286115</t>
+        </is>
+      </c>
+      <c r="L523" t="inlineStr">
+        <is>
+          <t>-40.950792919827684,172.0987754896828</t>
+        </is>
+      </c>
+      <c r="M523" t="inlineStr">
+        <is>
+          <t>-40.95011351633598,172.09874342880056</t>
+        </is>
+      </c>
+      <c r="N523" t="inlineStr">
+        <is>
+          <t>-40.94943591866021,172.09868724868252</t>
+        </is>
+      </c>
+      <c r="O523" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-23 22:18:30+00:00</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>-40.957515443026054,172.10033560867578</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>-40.95684355067395,172.1002011794665</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>-40.956146601253735,172.10022431853315</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>-40.95547741349401,172.10007279145734</t>
+        </is>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>-40.954825430837296,172.09981300223367</t>
+        </is>
+      </c>
+      <c r="G524" t="inlineStr">
+        <is>
+          <t>-40.95414789208569,172.09971391873555</t>
+        </is>
+      </c>
+      <c r="H524" t="inlineStr">
+        <is>
+          <t>-40.95334483434205,172.10040427526937</t>
+        </is>
+      </c>
+      <c r="I524" t="inlineStr">
+        <is>
+          <t>-40.95280614702819,172.0994009449229</t>
+        </is>
+      </c>
+      <c r="J524" t="inlineStr">
+        <is>
+          <t>-40.95213705030234,172.09914930933485</t>
+        </is>
+      </c>
+      <c r="K524" t="inlineStr">
+        <is>
+          <t>-40.951462719819084,172.09893523648452</t>
+        </is>
+      </c>
+      <c r="L524" t="inlineStr">
+        <is>
+          <t>-40.95079373731274,172.09876461273504</t>
+        </is>
+      </c>
+      <c r="M524" t="inlineStr">
+        <is>
+          <t>-40.95011441379344,172.09873148792616</t>
+        </is>
+      </c>
+      <c r="N524" t="inlineStr">
+        <is>
+          <t>-40.94943516337443,172.09869729783034</t>
+        </is>
+      </c>
+      <c r="O524" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0329/nzd0329.xlsx
+++ b/data/nzd0329/nzd0329.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O524"/>
+  <dimension ref="A1:O529"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26994,13 +26994,13 @@
         <v>408.24</v>
       </c>
       <c r="C524" t="n">
-        <v>403.41</v>
+        <v>396</v>
       </c>
       <c r="D524" t="n">
-        <v>385.03</v>
+        <v>372.21</v>
       </c>
       <c r="E524" t="n">
-        <v>381.67</v>
+        <v>368.59</v>
       </c>
       <c r="F524" t="n">
         <v>387.62</v>
@@ -27030,6 +27030,261 @@
         <v>388.39</v>
       </c>
       <c r="O524" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-24 22:12:29+00:00</t>
+        </is>
+      </c>
+      <c r="B525" t="n">
+        <v>407.8</v>
+      </c>
+      <c r="C525" t="n">
+        <v>389.65</v>
+      </c>
+      <c r="D525" t="n">
+        <v>361.11</v>
+      </c>
+      <c r="E525" t="n">
+        <v>357.93</v>
+      </c>
+      <c r="F525" t="n">
+        <v>387.62</v>
+      </c>
+      <c r="G525" t="n">
+        <v>379.75</v>
+      </c>
+      <c r="H525" t="n">
+        <v>303.99</v>
+      </c>
+      <c r="I525" t="n">
+        <v>373.79</v>
+      </c>
+      <c r="J525" t="n">
+        <v>382.34</v>
+      </c>
+      <c r="K525" t="n">
+        <v>392.33</v>
+      </c>
+      <c r="L525" t="n">
+        <v>398.74</v>
+      </c>
+      <c r="M525" t="n">
+        <v>393.52</v>
+      </c>
+      <c r="N525" t="n">
+        <v>388.39</v>
+      </c>
+      <c r="O525" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:18:27+00:00</t>
+        </is>
+      </c>
+      <c r="B526" t="n">
+        <v>408.02</v>
+      </c>
+      <c r="C526" t="n">
+        <v>380.5</v>
+      </c>
+      <c r="D526" t="n">
+        <v>347.9</v>
+      </c>
+      <c r="E526" t="n">
+        <v>346.04</v>
+      </c>
+      <c r="F526" t="n">
+        <v>390.27</v>
+      </c>
+      <c r="G526" t="n">
+        <v>380.88</v>
+      </c>
+      <c r="H526" t="n">
+        <v>299</v>
+      </c>
+      <c r="I526" t="n">
+        <v>375.3</v>
+      </c>
+      <c r="J526" t="n">
+        <v>384.26</v>
+      </c>
+      <c r="K526" t="n">
+        <v>395.73</v>
+      </c>
+      <c r="L526" t="n">
+        <v>401.8</v>
+      </c>
+      <c r="M526" t="n">
+        <v>395.7</v>
+      </c>
+      <c r="N526" t="n">
+        <v>391.69</v>
+      </c>
+      <c r="O526" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:12:05+00:00</t>
+        </is>
+      </c>
+      <c r="B527" t="n">
+        <v>407.92</v>
+      </c>
+      <c r="C527" t="n">
+        <v>374.79</v>
+      </c>
+      <c r="D527" t="n">
+        <v>339.3</v>
+      </c>
+      <c r="E527" t="n">
+        <v>337.14</v>
+      </c>
+      <c r="F527" t="n">
+        <v>390.27</v>
+      </c>
+      <c r="G527" t="n">
+        <v>380.88</v>
+      </c>
+      <c r="H527" t="n">
+        <v>299</v>
+      </c>
+      <c r="I527" t="n">
+        <v>375.3</v>
+      </c>
+      <c r="J527" t="n">
+        <v>384.26</v>
+      </c>
+      <c r="K527" t="n">
+        <v>395.73</v>
+      </c>
+      <c r="L527" t="n">
+        <v>401.8</v>
+      </c>
+      <c r="M527" t="n">
+        <v>395.7</v>
+      </c>
+      <c r="N527" t="n">
+        <v>391.69</v>
+      </c>
+      <c r="O527" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:12:23+00:00</t>
+        </is>
+      </c>
+      <c r="B528" t="n">
+        <v>408</v>
+      </c>
+      <c r="C528" t="n">
+        <v>371.23</v>
+      </c>
+      <c r="D528" t="n">
+        <v>333.04</v>
+      </c>
+      <c r="E528" t="n">
+        <v>330.92</v>
+      </c>
+      <c r="F528" t="n">
+        <v>390.27</v>
+      </c>
+      <c r="G528" t="n">
+        <v>380.88</v>
+      </c>
+      <c r="H528" t="n">
+        <v>299</v>
+      </c>
+      <c r="I528" t="n">
+        <v>375.3</v>
+      </c>
+      <c r="J528" t="n">
+        <v>384.26</v>
+      </c>
+      <c r="K528" t="n">
+        <v>395.73</v>
+      </c>
+      <c r="L528" t="n">
+        <v>401.8</v>
+      </c>
+      <c r="M528" t="n">
+        <v>395.7</v>
+      </c>
+      <c r="N528" t="n">
+        <v>391.69</v>
+      </c>
+      <c r="O528" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-24 22:18:38+00:00</t>
+        </is>
+      </c>
+      <c r="B529" t="n">
+        <v>408</v>
+      </c>
+      <c r="C529" t="n">
+        <v>371.23</v>
+      </c>
+      <c r="D529" t="n">
+        <v>325.99</v>
+      </c>
+      <c r="E529" t="n">
+        <v>324.4</v>
+      </c>
+      <c r="F529" t="n">
+        <v>390.27</v>
+      </c>
+      <c r="G529" t="n">
+        <v>380.88</v>
+      </c>
+      <c r="H529" t="n">
+        <v>299</v>
+      </c>
+      <c r="I529" t="n">
+        <v>375.3</v>
+      </c>
+      <c r="J529" t="n">
+        <v>384.26</v>
+      </c>
+      <c r="K529" t="n">
+        <v>395.73</v>
+      </c>
+      <c r="L529" t="n">
+        <v>401.8</v>
+      </c>
+      <c r="M529" t="n">
+        <v>395.7</v>
+      </c>
+      <c r="N529" t="n">
+        <v>391.69</v>
+      </c>
+      <c r="O529" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -27046,7 +27301,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B548"/>
+  <dimension ref="A1:B553"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32529,6 +32784,56 @@
       </c>
       <c r="B548" t="n">
         <v>-0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>2026-05-24 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B549" t="n">
+        <v>-0.63</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B550" t="n">
+        <v>-0.93</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B551" t="n">
+        <v>-0.76</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B552" t="n">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>2026-06-24 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B553" t="n">
+        <v>-0.22</v>
       </c>
     </row>
   </sheetData>
@@ -32697,28 +33002,28 @@
         <v>0.06519999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.391809855223474</v>
+        <v>-1.378531037242996</v>
       </c>
       <c r="J2" t="n">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="K2" t="n">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5277820817684782</v>
+        <v>0.5262562900959735</v>
       </c>
       <c r="M2" t="n">
-        <v>7.944432085301695</v>
+        <v>7.912232002063799</v>
       </c>
       <c r="N2" t="n">
-        <v>106.5926427460222</v>
+        <v>106.1653004119393</v>
       </c>
       <c r="O2" t="n">
-        <v>10.32437130027888</v>
+        <v>10.30365471140892</v>
       </c>
       <c r="P2" t="n">
-        <v>437.3107092114827</v>
+        <v>437.1750861290079</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -32775,28 +33080,28 @@
         <v>0.0912</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.369947966604256</v>
+        <v>-1.381978432971564</v>
       </c>
       <c r="J3" t="n">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="K3" t="n">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3806883899879494</v>
+        <v>0.3888426097642891</v>
       </c>
       <c r="M3" t="n">
-        <v>10.57963896493509</v>
+        <v>10.54859735673833</v>
       </c>
       <c r="N3" t="n">
-        <v>188.8647487878771</v>
+        <v>187.3694193519602</v>
       </c>
       <c r="O3" t="n">
-        <v>13.74280716549123</v>
+        <v>13.68829497607208</v>
       </c>
       <c r="P3" t="n">
-        <v>419.9672831242598</v>
+        <v>420.0896806702435</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32853,28 +33158,28 @@
         <v>0.081</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.570292009044085</v>
+        <v>-1.60625917716103</v>
       </c>
       <c r="J4" t="n">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="K4" t="n">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09749376788443764</v>
+        <v>0.1029980519824513</v>
       </c>
       <c r="M4" t="n">
-        <v>29.93651068777848</v>
+        <v>29.84246313077564</v>
       </c>
       <c r="N4" t="n">
-        <v>1416.144278466618</v>
+        <v>1406.544050347524</v>
       </c>
       <c r="O4" t="n">
-        <v>37.63169247411839</v>
+        <v>37.50392046636624</v>
       </c>
       <c r="P4" t="n">
-        <v>402.6545674193258</v>
+        <v>403.0200515276786</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32931,28 +33236,28 @@
         <v>0.06569999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.260388436384909</v>
+        <v>-2.280106520625804</v>
       </c>
       <c r="J5" t="n">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="K5" t="n">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1897176189213363</v>
+        <v>0.1952355329888452</v>
       </c>
       <c r="M5" t="n">
-        <v>29.10761537262651</v>
+        <v>28.94231568167413</v>
       </c>
       <c r="N5" t="n">
-        <v>1318.974950949942</v>
+        <v>1306.970399375806</v>
       </c>
       <c r="O5" t="n">
-        <v>36.3176947361743</v>
+        <v>36.15204557664485</v>
       </c>
       <c r="P5" t="n">
-        <v>408.8580453808071</v>
+        <v>409.0629498352688</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -33009,28 +33314,28 @@
         <v>0.0479</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.84618338134426</v>
+        <v>-0.8265572348291973</v>
       </c>
       <c r="J6" t="n">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="K6" t="n">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="L6" t="n">
-        <v>0.06304168967105972</v>
+        <v>0.06127466148182958</v>
       </c>
       <c r="M6" t="n">
-        <v>15.69858504318312</v>
+        <v>15.59172135375245</v>
       </c>
       <c r="N6" t="n">
-        <v>643.3552427429711</v>
+        <v>638.334653659175</v>
       </c>
       <c r="O6" t="n">
-        <v>25.36444840210351</v>
+        <v>25.26528554477814</v>
       </c>
       <c r="P6" t="n">
-        <v>400.9509970529014</v>
+        <v>400.7463344610885</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -33087,28 +33392,28 @@
         <v>0.0721</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.7340052919125674</v>
+        <v>-0.7351459234962794</v>
       </c>
       <c r="J7" t="n">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="K7" t="n">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1403958085233625</v>
+        <v>0.1430234348825171</v>
       </c>
       <c r="M7" t="n">
-        <v>8.320026363991282</v>
+        <v>8.246726413023744</v>
       </c>
       <c r="N7" t="n">
-        <v>203.2176511021464</v>
+        <v>201.2738470938907</v>
       </c>
       <c r="O7" t="n">
-        <v>14.25544285885733</v>
+        <v>14.18710143383386</v>
       </c>
       <c r="P7" t="n">
-        <v>401.0166348854711</v>
+        <v>401.0282997803439</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33165,28 +33470,28 @@
         <v>0.0625</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.9808550620249999</v>
+        <v>-1.105524441085617</v>
       </c>
       <c r="J8" t="n">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="K8" t="n">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="L8" t="n">
-        <v>0.320517044088991</v>
+        <v>0.3016010269764938</v>
       </c>
       <c r="M8" t="n">
-        <v>7.478426124275944</v>
+        <v>8.338867338305553</v>
       </c>
       <c r="N8" t="n">
-        <v>124.5409540276965</v>
+        <v>174.3743193625477</v>
       </c>
       <c r="O8" t="n">
-        <v>11.15979184517778</v>
+        <v>13.20508687447938</v>
       </c>
       <c r="P8" t="n">
-        <v>400.2989742641237</v>
+        <v>401.5822125537202</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -33243,28 +33548,28 @@
         <v>0.1418</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.9342728871254823</v>
+        <v>-0.9236922732818832</v>
       </c>
       <c r="J9" t="n">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="K9" t="n">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4198279708757948</v>
+        <v>0.4175706018838818</v>
       </c>
       <c r="M9" t="n">
-        <v>6.145318237460524</v>
+        <v>6.140697439192214</v>
       </c>
       <c r="N9" t="n">
-        <v>73.99706488375642</v>
+        <v>73.66405237981772</v>
       </c>
       <c r="O9" t="n">
-        <v>8.602154665184557</v>
+        <v>8.582776495972485</v>
       </c>
       <c r="P9" t="n">
-        <v>393.7391963987623</v>
+        <v>393.6307567355855</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -33321,28 +33626,28 @@
         <v>0.1123</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.8347267230091012</v>
+        <v>-0.8103010616157436</v>
       </c>
       <c r="J10" t="n">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="K10" t="n">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3845358359009077</v>
+        <v>0.3682157631141806</v>
       </c>
       <c r="M10" t="n">
-        <v>6.2020967356707</v>
+        <v>6.269817974806777</v>
       </c>
       <c r="N10" t="n">
-        <v>68.41261189445972</v>
+        <v>69.73436296737067</v>
       </c>
       <c r="O10" t="n">
-        <v>8.271191685268798</v>
+        <v>8.350710327114136</v>
       </c>
       <c r="P10" t="n">
-        <v>391.6945614891376</v>
+        <v>391.4442391650621</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -33399,28 +33704,28 @@
         <v>0.0985</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.8758453158398998</v>
+        <v>-0.8494328838249924</v>
       </c>
       <c r="J11" t="n">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="K11" t="n">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2912691328614007</v>
+        <v>0.2784557525194946</v>
       </c>
       <c r="M11" t="n">
-        <v>8.282959864727792</v>
+        <v>8.344365848531748</v>
       </c>
       <c r="N11" t="n">
-        <v>114.5046947761306</v>
+        <v>115.7317516321314</v>
       </c>
       <c r="O11" t="n">
-        <v>10.70068664974966</v>
+        <v>10.75786928867103</v>
       </c>
       <c r="P11" t="n">
-        <v>402.7817601794532</v>
+        <v>402.5110659524281</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -33477,28 +33782,28 @@
         <v>0.1001</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.9736446006900482</v>
+        <v>-0.9420856870932781</v>
       </c>
       <c r="J12" t="n">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="K12" t="n">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2850653995206816</v>
+        <v>0.2710761298164163</v>
       </c>
       <c r="M12" t="n">
-        <v>9.575235189269826</v>
+        <v>9.638673284833724</v>
       </c>
       <c r="N12" t="n">
-        <v>145.2925969924028</v>
+        <v>147.1720760313425</v>
       </c>
       <c r="O12" t="n">
-        <v>12.05373788467307</v>
+        <v>12.13144987342166</v>
       </c>
       <c r="P12" t="n">
-        <v>408.5974898639354</v>
+        <v>408.2731905207748</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -33555,28 +33860,28 @@
         <v>0.137</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.7293647844130703</v>
+        <v>-0.6983657952202896</v>
       </c>
       <c r="J13" t="n">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="K13" t="n">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1998677182949983</v>
+        <v>0.1854798254841922</v>
       </c>
       <c r="M13" t="n">
-        <v>8.768695590630337</v>
+        <v>8.828268991813562</v>
       </c>
       <c r="N13" t="n">
-        <v>129.8587529381956</v>
+        <v>131.7705470517232</v>
       </c>
       <c r="O13" t="n">
-        <v>11.39555847416859</v>
+        <v>11.4791352919862</v>
       </c>
       <c r="P13" t="n">
-        <v>396.45044026592</v>
+        <v>396.1307608725444</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -33633,28 +33938,28 @@
         <v>0.1005</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.8751796308696761</v>
+        <v>-0.8486558421045337</v>
       </c>
       <c r="J14" t="n">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="K14" t="n">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="L14" t="n">
-        <v>0.3003604376979252</v>
+        <v>0.2870133601304495</v>
       </c>
       <c r="M14" t="n">
-        <v>8.133756209495431</v>
+        <v>8.189003734074866</v>
       </c>
       <c r="N14" t="n">
-        <v>109.4506929817794</v>
+        <v>110.7409690064953</v>
       </c>
       <c r="O14" t="n">
-        <v>10.46186852248581</v>
+        <v>10.52335350572693</v>
       </c>
       <c r="P14" t="n">
-        <v>398.7187432726634</v>
+        <v>398.4464288302571</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -33692,7 +33997,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O524"/>
+  <dimension ref="A1:O529"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73687,17 +73992,17 @@
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>-40.95684355067395,172.1002011794665</t>
+          <t>-40.95682985145573,172.10028734928525</t>
         </is>
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>-40.956146601253735,172.10022431853315</t>
+          <t>-40.956122900142816,172.1003733988357</t>
         </is>
       </c>
       <c r="E524" t="inlineStr">
         <is>
-          <t>-40.95547741349401,172.10007279145734</t>
+          <t>-40.95545323180425,172.10022489371696</t>
         </is>
       </c>
       <c r="F524" t="inlineStr">
@@ -73746,6 +74051,391 @@
         </is>
       </c>
       <c r="O524" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-24 22:12:29+00:00</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>-40.95751462957638,172.1003407254244</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>-40.95681811185818,172.10036119248977</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>-40.956102378743424,172.10050247764127</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>-40.9554335239475,172.10034885465333</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>-40.954825430837296,172.09981300223367</t>
+        </is>
+      </c>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>-40.95414789208569,172.09971391873555</t>
+        </is>
+      </c>
+      <c r="H525" t="inlineStr">
+        <is>
+          <t>-40.95334483434205,172.10040427526937</t>
+        </is>
+      </c>
+      <c r="I525" t="inlineStr">
+        <is>
+          <t>-40.95280614702819,172.0994009449229</t>
+        </is>
+      </c>
+      <c r="J525" t="inlineStr">
+        <is>
+          <t>-40.95213705030234,172.09914930933485</t>
+        </is>
+      </c>
+      <c r="K525" t="inlineStr">
+        <is>
+          <t>-40.951462719819084,172.09893523648452</t>
+        </is>
+      </c>
+      <c r="L525" t="inlineStr">
+        <is>
+          <t>-40.95079373731274,172.09876461273504</t>
+        </is>
+      </c>
+      <c r="M525" t="inlineStr">
+        <is>
+          <t>-40.95011441379344,172.09873148792616</t>
+        </is>
+      </c>
+      <c r="N525" t="inlineStr">
+        <is>
+          <t>-40.94943516337443,172.09869729783034</t>
+        </is>
+      </c>
+      <c r="O525" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:18:27+00:00</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>-40.95751503630125,172.1003381670501</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>-40.956801195661484,172.10046759643282</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>-40.956077956239845,172.10065609294776</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>-40.95541154194905,172.10048711869032</t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>-40.954830329958696,172.09978218668647</t>
+        </is>
+      </c>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>-40.95414998114331,172.09970077865538</t>
+        </is>
+      </c>
+      <c r="H526" t="inlineStr">
+        <is>
+          <t>-40.953335608805595,172.10046230011994</t>
+        </is>
+      </c>
+      <c r="I526" t="inlineStr">
+        <is>
+          <t>-40.95280862576167,172.0993833049182</t>
+        </is>
+      </c>
+      <c r="J526" t="inlineStr">
+        <is>
+          <t>-40.952139279854336,172.09912668824202</t>
+        </is>
+      </c>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>-40.95146574099531,172.09889503866572</t>
+        </is>
+      </c>
+      <c r="L526" t="inlineStr">
+        <is>
+          <t>-40.95079645633172,172.09872843505914</t>
+        </is>
+      </c>
+      <c r="M526" t="inlineStr">
+        <is>
+          <t>-40.95011635087563,172.09870571455264</t>
+        </is>
+      </c>
+      <c r="N526" t="inlineStr">
+        <is>
+          <t>-40.94943809565543,172.0986582834905</t>
+        </is>
+      </c>
+      <c r="O526" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:12:05+00:00</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>-40.95751485142632,172.1003393299475</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>-40.956790639165156,172.10053399711813</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>-40.95606205654318,172.10075609982562</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>-40.955395087694676,172.10059061315945</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>-40.954830329958696,172.09978218668647</t>
+        </is>
+      </c>
+      <c r="G527" t="inlineStr">
+        <is>
+          <t>-40.95414998114331,172.09970077865538</t>
+        </is>
+      </c>
+      <c r="H527" t="inlineStr">
+        <is>
+          <t>-40.953335608805595,172.10046230011994</t>
+        </is>
+      </c>
+      <c r="I527" t="inlineStr">
+        <is>
+          <t>-40.95280862576167,172.0993833049182</t>
+        </is>
+      </c>
+      <c r="J527" t="inlineStr">
+        <is>
+          <t>-40.952139279854336,172.09912668824202</t>
+        </is>
+      </c>
+      <c r="K527" t="inlineStr">
+        <is>
+          <t>-40.95146574099531,172.09889503866572</t>
+        </is>
+      </c>
+      <c r="L527" t="inlineStr">
+        <is>
+          <t>-40.95079645633172,172.09872843505914</t>
+        </is>
+      </c>
+      <c r="M527" t="inlineStr">
+        <is>
+          <t>-40.95011635087563,172.09870571455264</t>
+        </is>
+      </c>
+      <c r="N527" t="inlineStr">
+        <is>
+          <t>-40.94943809565543,172.0986582834905</t>
+        </is>
+      </c>
+      <c r="O527" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:12:23+00:00</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>-40.95751499932625,172.10033839962958</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>-40.956784057512245,172.10057539578375</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>-40.956050482988154,172.10082889550048</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>-40.95538358814902,172.10066294297238</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>-40.954830329958696,172.09978218668647</t>
+        </is>
+      </c>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>-40.95414998114331,172.09970077865538</t>
+        </is>
+      </c>
+      <c r="H528" t="inlineStr">
+        <is>
+          <t>-40.953335608805595,172.10046230011994</t>
+        </is>
+      </c>
+      <c r="I528" t="inlineStr">
+        <is>
+          <t>-40.95280862576167,172.0993833049182</t>
+        </is>
+      </c>
+      <c r="J528" t="inlineStr">
+        <is>
+          <t>-40.952139279854336,172.09912668824202</t>
+        </is>
+      </c>
+      <c r="K528" t="inlineStr">
+        <is>
+          <t>-40.95146574099531,172.09889503866572</t>
+        </is>
+      </c>
+      <c r="L528" t="inlineStr">
+        <is>
+          <t>-40.95079645633172,172.09872843505914</t>
+        </is>
+      </c>
+      <c r="M528" t="inlineStr">
+        <is>
+          <t>-40.95011635087563,172.09870571455264</t>
+        </is>
+      </c>
+      <c r="N528" t="inlineStr">
+        <is>
+          <t>-40.94943809565543,172.0986582834905</t>
+        </is>
+      </c>
+      <c r="O528" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-24 22:18:38+00:00</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>-40.95751499932625,172.10033839962958</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>-40.956784057512245,172.10057539578375</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>-40.95603744881728,172.10091087782052</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>-40.955371533913905,172.10073876133538</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>-40.954830329958696,172.09978218668647</t>
+        </is>
+      </c>
+      <c r="G529" t="inlineStr">
+        <is>
+          <t>-40.95414998114331,172.09970077865538</t>
+        </is>
+      </c>
+      <c r="H529" t="inlineStr">
+        <is>
+          <t>-40.953335608805595,172.10046230011994</t>
+        </is>
+      </c>
+      <c r="I529" t="inlineStr">
+        <is>
+          <t>-40.95280862576167,172.0993833049182</t>
+        </is>
+      </c>
+      <c r="J529" t="inlineStr">
+        <is>
+          <t>-40.952139279854336,172.09912668824202</t>
+        </is>
+      </c>
+      <c r="K529" t="inlineStr">
+        <is>
+          <t>-40.95146574099531,172.09889503866572</t>
+        </is>
+      </c>
+      <c r="L529" t="inlineStr">
+        <is>
+          <t>-40.95079645633172,172.09872843505914</t>
+        </is>
+      </c>
+      <c r="M529" t="inlineStr">
+        <is>
+          <t>-40.95011635087563,172.09870571455264</t>
+        </is>
+      </c>
+      <c r="N529" t="inlineStr">
+        <is>
+          <t>-40.94943809565543,172.0986582834905</t>
+        </is>
+      </c>
+      <c r="O529" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
